--- a/data/trending_integrated_20261030_14.xlsx
+++ b/data/trending_integrated_20261030_14.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24000</v>
+        <v>24050</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+166.67%</t>
+          <t>'+167.22%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G2" t="n">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>807661959915</v>
+        <v>820316737265</v>
       </c>
       <c r="P2" t="n">
         <v>27100</v>
@@ -622,20 +622,20 @@
         <v>-174000</v>
       </c>
       <c r="S2" t="n">
-        <v>-90000</v>
+        <v>-88000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>정부 지원 AI 회사로 향후 IPO 대장주 가능성 언급. 신규 상장 후 변동성이 크며, 개인 투자자들의 단타 지양 권고.</t>
+          <t>AI 관련주로 정부 지원 기대감 속 급등락 반복. 투자 주의 및 관망 의견.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', 'IPO', '신규 상장']</t>
+          <t>['AI', 'IPO', '패턴']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>36494696300</v>
+        <v>37084301485</v>
       </c>
       <c r="P3" t="n">
         <v>16620</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>지수 급락 속 상한가 기대감. 건설업 활성화와 주포의 움직임 관찰. 유증 성공 여부 주목.</t>
+          <t>건설업 경기 회복 기대감 속 주가 상승 시도. 유증 성공 및 주가 조작 의혹.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['상한가', '건설', '주포']</t>
+          <t>['건설', '유증', '주포']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19590</v>
+        <v>19500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.66%</t>
+          <t>'+17.12%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F4" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G4" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -794,7 +794,7 @@
         <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>131390713125</v>
+        <v>133277366325</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -806,20 +806,20 @@
         <v>67000</v>
       </c>
       <c r="S4" t="n">
-        <v>23000</v>
+        <v>28000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부의 양자 보안 의무화 정책 및 바이낸스/빗썸 해킹 사태로 인한 라온시큐어의 최대 수혜주로서의 기대감 상승. 기술력 및 보안 대장주로서의 전망.</t>
+          <t>정부 양자 보안 의무화 및 바이낸스, 빗썸 해킹 사태로 인한 최대 수혜주 부각. 기술력 및 수혜 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자 보안', '해킹', '수혜주']</t>
+          <t>['양자보안', '해킹', '수혜주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>진양화학</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2815</v>
+        <v>8840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.90%</t>
+          <t>'+14.81%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="E5" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="H5" t="n">
-        <v>0.79</v>
+        <v>13.29</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2450</v>
+        <v>7700</v>
       </c>
       <c r="K5" t="n">
-        <v>2460</v>
+        <v>9360</v>
       </c>
       <c r="L5" t="n">
-        <v>3110</v>
+        <v>9500</v>
       </c>
       <c r="M5" t="n">
-        <v>2335</v>
+        <v>8430</v>
       </c>
       <c r="N5" t="n">
-        <v>0.63</v>
+        <v>12.92</v>
       </c>
       <c r="O5" t="n">
-        <v>12872262766</v>
+        <v>9363482855</v>
       </c>
       <c r="P5" t="n">
-        <v>3170</v>
+        <v>13670</v>
       </c>
       <c r="Q5" t="n">
-        <v>880</v>
+        <v>7060</v>
       </c>
       <c r="R5" t="n">
-        <v>-23000</v>
+        <v>-44000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
+          <t>임상 3상 성공에도 불구하고 주가 부진. 시장 규모 및 경쟁 업체 고려 시 큰 호재 아님.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
+          <t>['임상 3상', '위식도염', '시장 규모']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>051630</t>
+          <t>003220</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8770</v>
+        <v>2810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.90%</t>
+          <t>'+14.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.37</v>
+        <v>0.16</v>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>126</v>
+        <v>37</v>
       </c>
       <c r="H6" t="n">
-        <v>13.29</v>
+        <v>0.79</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7700</v>
+        <v>2450</v>
       </c>
       <c r="K6" t="n">
-        <v>9360</v>
+        <v>2460</v>
       </c>
       <c r="L6" t="n">
-        <v>9500</v>
+        <v>3110</v>
       </c>
       <c r="M6" t="n">
-        <v>8430</v>
+        <v>2335</v>
       </c>
       <c r="N6" t="n">
-        <v>12.92</v>
+        <v>0.63</v>
       </c>
       <c r="O6" t="n">
-        <v>9146273145</v>
+        <v>12930487922</v>
       </c>
       <c r="P6" t="n">
-        <v>13670</v>
+        <v>3170</v>
       </c>
       <c r="Q6" t="n">
-        <v>7060</v>
+        <v>880</v>
       </c>
       <c r="R6" t="n">
-        <v>-70000</v>
+        <v>-24000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>임상 3상 성공에도 불구하고 주가 부진. 시장 규모 및 경쟁 업체 고려 시 큰 호재 아님.</t>
+          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['임상 3상', '위식도염', '시장 규모']</t>
+          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>003220</t>
+          <t>051630</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11930</v>
+        <v>11840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.52%</t>
+          <t>'+5.71%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F7" t="n">
         <v>199</v>
       </c>
       <c r="G7" t="n">
-        <v>951</v>
+        <v>983</v>
       </c>
       <c r="H7" t="n">
         <v>15.04</v>
@@ -1070,7 +1070,7 @@
         <v>15.08</v>
       </c>
       <c r="O7" t="n">
-        <v>58461864395</v>
+        <v>59006481950</v>
       </c>
       <c r="P7" t="n">
         <v>18960</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>서울반도체의 혁신 기술 개발 및 시장 석권 기대감. 희토류 없는 백색 LED 개발 성공. 공매도 폐지 요구 및 주가 상승 전망.</t>
+          <t>세계 최초 희토류 없는 백색 LED 개발 성공 및 100억 달러 시장 석권 전망. 기술력 기반 주가 우상향 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['백색 LED', '희토류', '공매도']</t>
+          <t>['백색LED', '희토류', '기술개발']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51900</v>
+        <v>51800</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.70%</t>
+          <t>'+5.50%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.82</v>
       </c>
       <c r="E8" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H8" t="n">
         <v>23.82</v>
@@ -1162,7 +1162,7 @@
         <v>24.64</v>
       </c>
       <c r="O8" t="n">
-        <v>65946138750</v>
+        <v>68325986450</v>
       </c>
       <c r="P8" t="n">
         <v>97900</v>
@@ -1171,10 +1171,10 @@
         <v>30950</v>
       </c>
       <c r="R8" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="S8" t="n">
-        <v>69000</v>
+        <v>80000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15680</v>
+        <v>15690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.67%</t>
+          <t>'+4.74%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.9</v>
       </c>
       <c r="E9" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G9" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="H9" t="n">
         <v>7.15</v>
@@ -1254,7 +1254,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>54280673515</v>
+        <v>54967663705</v>
       </c>
       <c r="P9" t="n">
         <v>49800</v>
@@ -1263,10 +1263,10 @@
         <v>8180</v>
       </c>
       <c r="R9" t="n">
-        <v>101000</v>
+        <v>84000</v>
       </c>
       <c r="S9" t="n">
-        <v>189000</v>
+        <v>179000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29150</v>
+        <v>29050</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.92%</t>
+          <t>'+3.57%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="H10" t="n">
         <v>4.69</v>
@@ -1346,7 +1346,7 @@
         <v>5.05</v>
       </c>
       <c r="O10" t="n">
-        <v>125449388500</v>
+        <v>126330952775</v>
       </c>
       <c r="P10" t="n">
         <v>50600</v>
@@ -1355,10 +1355,10 @@
         <v>13210</v>
       </c>
       <c r="R10" t="n">
-        <v>-12000</v>
+        <v>-40000</v>
       </c>
       <c r="S10" t="n">
-        <v>188000</v>
+        <v>228000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1391,70 +1391,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15740</v>
+        <v>4045</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.13%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.06</v>
+        <v>-0.77</v>
       </c>
       <c r="E11" t="n">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>333</v>
+        <v>209</v>
       </c>
       <c r="H11" t="n">
-        <v>28.13</v>
+        <v>1.43</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>15720</v>
+        <v>4040</v>
       </c>
       <c r="K11" t="n">
-        <v>15420</v>
+        <v>3925</v>
       </c>
       <c r="L11" t="n">
-        <v>16050</v>
+        <v>4265</v>
       </c>
       <c r="M11" t="n">
-        <v>15320</v>
+        <v>3880</v>
       </c>
       <c r="N11" t="n">
-        <v>28.07</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>52465919690</v>
+        <v>82572158540</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>8100</v>
       </c>
       <c r="Q11" t="n">
-        <v>15320</v>
+        <v>592</v>
       </c>
       <c r="R11" t="n">
-        <v>700000</v>
+        <v>78000</v>
       </c>
       <c r="S11" t="n">
-        <v>-15000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국내 조선주 약세 속 미국 조선주 HII 폭등 비교. 3분기 실적 서프라이즈 기대와 정기선 승계 및 증여세와의 상관관계 의문 제기.</t>
+          <t>국내 시장 폭락 속에서도 견조한 흐름 보이는 빛과전자. 50층 돌파 및 6천원 도달 기대감. 외국인, 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선주', '실적', '승계']</t>
+          <t>['상승', '기대감', '외국인매수']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,169 +1476,169 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4025</v>
+        <v>15715</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.37%</t>
+          <t>'-0.03%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.77</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="G12" t="n">
-        <v>209</v>
+        <v>351</v>
       </c>
       <c r="H12" t="n">
-        <v>1.43</v>
+        <v>28.13</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4040</v>
+        <v>15720</v>
       </c>
       <c r="K12" t="n">
-        <v>3925</v>
+        <v>15420</v>
       </c>
       <c r="L12" t="n">
-        <v>4265</v>
+        <v>16050</v>
       </c>
       <c r="M12" t="n">
-        <v>3880</v>
+        <v>15320</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>28.07</v>
       </c>
       <c r="O12" t="n">
-        <v>82005266157</v>
+        <v>54274481330</v>
       </c>
       <c r="P12" t="n">
-        <v>8100</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>592</v>
+        <v>15320</v>
       </c>
       <c r="R12" t="n">
-        <v>78000</v>
+        <v>788000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-71000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국내 시장 폭락 속에서도 견조한 흐름 보이는 빛과전자. 50층 돌파 및 6천원 도달 기대감. 외국인, 프로그램 매수세 관찰.</t>
+          <t>3분기 실적 서프라이즈 및 미국 조선주 강세 속 국내 조선주 약세 진단. 정기선 승계와 증여세 상관관계 의문 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['상승', '기대감', '외국인매수']</t>
+          <t>['실적', '조선주', '승계']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8420</v>
+        <v>7280</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'-2.28%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="F13" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="G13" t="n">
-        <v>297</v>
+        <v>248</v>
       </c>
       <c r="H13" t="n">
-        <v>2.67</v>
+        <v>25.3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8580</v>
+        <v>7450</v>
       </c>
       <c r="K13" t="n">
-        <v>11090</v>
+        <v>7350</v>
       </c>
       <c r="L13" t="n">
-        <v>11150</v>
+        <v>7570</v>
       </c>
       <c r="M13" t="n">
-        <v>8070</v>
+        <v>7250</v>
       </c>
       <c r="N13" t="n">
-        <v>2.66</v>
+        <v>25.32</v>
       </c>
       <c r="O13" t="n">
-        <v>30082977520</v>
+        <v>10732249525</v>
       </c>
       <c r="P13" t="n">
-        <v>19270</v>
+        <v>17950</v>
       </c>
       <c r="Q13" t="n">
-        <v>2135</v>
+        <v>7010</v>
       </c>
       <c r="R13" t="n">
-        <v>-381000</v>
+        <v>-46000</v>
       </c>
       <c r="S13" t="n">
-        <v>-1000</v>
+        <v>-8000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>서울바이오시스의 독점 기술 및 신규 기술(광통신, 와이캅3)에 대한 기대감 존재. 환기 문제 해소 및 외인 유입 가능성 언급.</t>
+          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광반도체', '와이캅3', '환기']</t>
+          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7290</v>
+        <v>61300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.15%</t>
+          <t>'-2.39%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>243</v>
+        <v>372</v>
       </c>
       <c r="H14" t="n">
-        <v>25.3</v>
+        <v>41.76</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7450</v>
+        <v>62800</v>
       </c>
       <c r="K14" t="n">
-        <v>7350</v>
+        <v>62300</v>
       </c>
       <c r="L14" t="n">
-        <v>7570</v>
+        <v>62800</v>
       </c>
       <c r="M14" t="n">
-        <v>7250</v>
+        <v>60700</v>
       </c>
       <c r="N14" t="n">
-        <v>25.32</v>
+        <v>41.55</v>
       </c>
       <c r="O14" t="n">
-        <v>10541184615</v>
+        <v>99578355250</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>67300</v>
       </c>
       <c r="Q14" t="n">
-        <v>7010</v>
+        <v>23150</v>
       </c>
       <c r="R14" t="n">
-        <v>76000</v>
+        <v>-65000</v>
       </c>
       <c r="S14" t="n">
-        <v>-7000</v>
+        <v>-81000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
+          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
+          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>61150</v>
+        <v>8310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.63%</t>
+          <t>'-3.15%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.21</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G15" t="n">
-        <v>351</v>
+        <v>300</v>
       </c>
       <c r="H15" t="n">
-        <v>41.76</v>
+        <v>2.67</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>62800</v>
+        <v>8580</v>
       </c>
       <c r="K15" t="n">
-        <v>62300</v>
+        <v>11090</v>
       </c>
       <c r="L15" t="n">
-        <v>62800</v>
+        <v>11150</v>
       </c>
       <c r="M15" t="n">
-        <v>60700</v>
+        <v>8070</v>
       </c>
       <c r="N15" t="n">
-        <v>41.55</v>
+        <v>2.66</v>
       </c>
       <c r="O15" t="n">
-        <v>96268444050</v>
+        <v>30200342665</v>
       </c>
       <c r="P15" t="n">
-        <v>67300</v>
+        <v>19270</v>
       </c>
       <c r="Q15" t="n">
-        <v>23150</v>
+        <v>2135</v>
       </c>
       <c r="R15" t="n">
-        <v>55000</v>
+        <v>-396000</v>
       </c>
       <c r="S15" t="n">
-        <v>-81000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
+          <t>서울바이오시스의 독점 기술 및 신규 기술(광통신, 와이캅3)에 대한 기대감 존재. 환기 문제 해소 및 외인 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
+          <t>['광반도체', '와이캅3', '환기']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>225500</v>
+        <v>224500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.80%</t>
+          <t>'-3.23%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="G16" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="H16" t="n">
         <v>46.17</v>
@@ -1898,7 +1898,7 @@
         <v>46.19</v>
       </c>
       <c r="O16" t="n">
-        <v>2991464489750</v>
+        <v>3075451193250</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1907,14 +1907,14 @@
         <v>94500</v>
       </c>
       <c r="R16" t="n">
-        <v>664000</v>
+        <v>538000</v>
       </c>
       <c r="S16" t="n">
-        <v>-505000</v>
+        <v>241000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>이재용 상속세 관련 정치적 논란과 주가 부양 의문 제기. 일부 게시글에서 주가 하락 원인으로 지목하며 경영진 퇴진 및 자사주 소각 요구.</t>
+          <t>이재용 경영 퇴진, 자사주 매입 소각 촉구. 정치적 이슈와 연계된 주가 부양 압박.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['상속세', '주가', '경영진']</t>
+          <t>['이재용', '상속세', '자사주']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,70 +1943,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>176500</v>
+        <v>6400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.02%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.13</v>
+        <v>-0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>256</v>
+        <v>84</v>
       </c>
       <c r="H17" t="n">
-        <v>74.87</v>
+        <v>0.85</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>183900</v>
+        <v>6640</v>
       </c>
       <c r="K17" t="n">
-        <v>176800</v>
+        <v>7210</v>
       </c>
       <c r="L17" t="n">
-        <v>179000</v>
+        <v>7500</v>
       </c>
       <c r="M17" t="n">
-        <v>168100</v>
+        <v>6230</v>
       </c>
       <c r="N17" t="n">
-        <v>75</v>
+        <v>0.9</v>
       </c>
       <c r="O17" t="n">
-        <v>645686665250</v>
+        <v>32201335060</v>
       </c>
       <c r="P17" t="n">
-        <v>243500</v>
+        <v>9820</v>
       </c>
       <c r="Q17" t="n">
-        <v>71000</v>
+        <v>4000</v>
       </c>
       <c r="R17" t="n">
-        <v>-658000</v>
+        <v>-55000</v>
       </c>
       <c r="S17" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 조작', '증여세', '우선주 소각']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
@@ -2050,13 +2050,13 @@
         <v>-0.63</v>
       </c>
       <c r="E18" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F18" t="n">
         <v>175</v>
       </c>
       <c r="G18" t="n">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="H18" t="n">
         <v>11.6</v>
@@ -2082,7 +2082,7 @@
         <v>12.23</v>
       </c>
       <c r="O18" t="n">
-        <v>88382099825</v>
+        <v>90360433675</v>
       </c>
       <c r="P18" t="n">
         <v>59300</v>
@@ -2091,10 +2091,10 @@
         <v>21100</v>
       </c>
       <c r="R18" t="n">
-        <v>-650000</v>
+        <v>-728000</v>
       </c>
       <c r="S18" t="n">
-        <v>-235000</v>
+        <v>-220000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2127,70 +2127,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6340</v>
+        <v>175200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.52%</t>
+          <t>'-4.73%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.05</v>
+        <v>-0.13</v>
       </c>
       <c r="E19" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="G19" t="n">
-        <v>83</v>
+        <v>258</v>
       </c>
       <c r="H19" t="n">
-        <v>0.85</v>
+        <v>74.87</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6640</v>
+        <v>183900</v>
       </c>
       <c r="K19" t="n">
-        <v>7210</v>
+        <v>176800</v>
       </c>
       <c r="L19" t="n">
-        <v>7500</v>
+        <v>179000</v>
       </c>
       <c r="M19" t="n">
-        <v>6230</v>
+        <v>168100</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9</v>
+        <v>75</v>
       </c>
       <c r="O19" t="n">
-        <v>32161822690</v>
+        <v>656836494450</v>
       </c>
       <c r="P19" t="n">
-        <v>9820</v>
+        <v>243500</v>
       </c>
       <c r="Q19" t="n">
-        <v>4000</v>
+        <v>71000</v>
       </c>
       <c r="R19" t="n">
-        <v>-55000</v>
+        <v>-802000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['주가 조작', '증여세', '우선주 소각']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>54050</v>
+        <v>53900</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.67%</t>
+          <t>'-4.94%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.2</v>
       </c>
       <c r="E20" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F20" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G20" t="n">
-        <v>1125</v>
+        <v>1168</v>
       </c>
       <c r="H20" t="n">
         <v>22.14</v>
@@ -2266,7 +2266,7 @@
         <v>22.34</v>
       </c>
       <c r="O20" t="n">
-        <v>90347129650</v>
+        <v>92299365650</v>
       </c>
       <c r="P20" t="n">
         <v>139200</v>
@@ -2275,10 +2275,10 @@
         <v>53400</v>
       </c>
       <c r="R20" t="n">
-        <v>-238000</v>
+        <v>-281000</v>
       </c>
       <c r="S20" t="n">
-        <v>-81000</v>
+        <v>-89000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1436500</v>
+        <v>11000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.87%</t>
+          <t>'-5.34%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>800</v>
+        <v>434</v>
       </c>
       <c r="F21" t="n">
-        <v>498</v>
+        <v>184</v>
       </c>
       <c r="G21" t="n">
-        <v>1249</v>
+        <v>1363</v>
       </c>
       <c r="H21" t="n">
-        <v>48.72</v>
+        <v>9.73</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,47 +2343,47 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1526000</v>
+        <v>11620</v>
       </c>
       <c r="K21" t="n">
-        <v>1444000</v>
+        <v>11300</v>
       </c>
       <c r="L21" t="n">
-        <v>1449000</v>
+        <v>11470</v>
       </c>
       <c r="M21" t="n">
-        <v>1381000</v>
+        <v>10890</v>
       </c>
       <c r="N21" t="n">
-        <v>48.66</v>
+        <v>9.6</v>
       </c>
       <c r="O21" t="n">
-        <v>3600162111000</v>
+        <v>59456553295</v>
       </c>
       <c r="P21" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q21" t="n">
-        <v>501000</v>
+        <v>3320</v>
       </c>
       <c r="R21" t="n">
-        <v>-202000</v>
+        <v>-504000</v>
       </c>
       <c r="S21" t="n">
-        <v>-107000</v>
+        <v>-81000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>샌디스크 실적 호조와 AI 투자 확대에 따른 기대감. 자사주 매입 및 5000억 영익 전망 언급. 일부 게시글은 주가 하락 우려.</t>
+          <t>원전 사업 및 가덕도 공사 관련 정부 정책 변화와 공매도 금지 조치가 호재로 해석. 한수원의 갑질 논란과 재건 사업 기회 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['AI 투자', '자사주 매입', '실적']</t>
+          <t>['원전', '공매도 금지', '가덕도']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10930</v>
+        <v>1422000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-5.94%</t>
+          <t>'-6.82%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="E22" t="n">
-        <v>424</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>182</v>
+        <v>486</v>
       </c>
       <c r="G22" t="n">
-        <v>1332</v>
+        <v>1222</v>
       </c>
       <c r="H22" t="n">
-        <v>9.73</v>
+        <v>48.72</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,47 +2435,47 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>11620</v>
+        <v>1526000</v>
       </c>
       <c r="K22" t="n">
-        <v>11300</v>
+        <v>1444000</v>
       </c>
       <c r="L22" t="n">
-        <v>11470</v>
+        <v>1449000</v>
       </c>
       <c r="M22" t="n">
-        <v>10890</v>
+        <v>1381000</v>
       </c>
       <c r="N22" t="n">
-        <v>9.6</v>
+        <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>57906983590</v>
+        <v>3694986184500</v>
       </c>
       <c r="P22" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q22" t="n">
-        <v>3320</v>
+        <v>501000</v>
       </c>
       <c r="R22" t="n">
-        <v>-450000</v>
+        <v>-177000</v>
       </c>
       <c r="S22" t="n">
-        <v>-75000</v>
+        <v>-59000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>원전 사업 및 가덕도 공사 관련 정부 정책 변화와 공매도 금지 조치가 호재로 해석. 한수원의 갑질 논란과 재건 사업 기회 언급.</t>
+          <t>샌디스크 역대급 서프라이즈 및 구글, 아마존 AI 투자 확대에 따른 SK하이닉스 실적 기대감. 외인 매수세 유입.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['원전', '공매도 금지', '가덕도']</t>
+          <t>['AI', '샌디스크', '실적']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13940</v>
+        <v>13850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-7.25%</t>
+          <t>'-7.85%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F23" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G23" t="n">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>47124156490</v>
+        <v>47817418555</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2551,14 +2551,14 @@
         <v>1830</v>
       </c>
       <c r="R23" t="n">
-        <v>-180000</v>
+        <v>-225000</v>
       </c>
       <c r="S23" t="n">
-        <v>-51000</v>
+        <v>-65000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>호재에도 불구하고 한국 증시 불신으로 인한 주가 하락. 27년까지의 장기 보유 및 전고점 돌파 기대감 언급.</t>
+          <t>광케이블 관련 특허 보유 및 호재에도 불구하고 국내 시장 불신으로 인한 주가 하락. 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['호재', '증시 불신', '장기 보유']</t>
+          <t>['광케이블', '특허', '정부']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7100</v>
+        <v>7110</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.13%</t>
+          <t>'-10.00%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F24" t="n">
         <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>16824880240</v>
+        <v>16903913275</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2643,7 +2643,7 @@
         <v>952</v>
       </c>
       <c r="R24" t="n">
-        <v>-28000</v>
+        <v>-33000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>119000</v>
+        <v>118000</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-13.89%</t>
+          <t>'-14.62%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F25" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G25" t="n">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2726,7 +2726,7 @@
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>184788177200</v>
+        <v>188499835950</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2735,10 +2735,10 @@
         <v>36450</v>
       </c>
       <c r="R25" t="n">
-        <v>-346000</v>
+        <v>-362000</v>
       </c>
       <c r="S25" t="n">
-        <v>-69000</v>
+        <v>-79000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14030</v>
+        <v>13890</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-17.47%</t>
+          <t>'-18.29%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="F26" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>66595293515</v>
+        <v>67486499370</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2830,7 +2830,7 @@
         <v>57000</v>
       </c>
       <c r="S26" t="n">
-        <v>-182000</v>
+        <v>-193000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>1.45</v>
       </c>
       <c r="E27" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F27" t="n">
         <v>55</v>
@@ -2910,7 +2910,7 @@
         <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>8294886022</v>
+        <v>8385265368</v>
       </c>
       <c r="P27" t="n">
         <v>5700</v>
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9950</v>
+        <v>9730</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-33.67%</t>
+          <t>'-35.13%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F28" t="n">
         <v>227</v>
       </c>
       <c r="G28" t="n">
-        <v>877</v>
+        <v>897</v>
       </c>
       <c r="H28" t="n">
         <v>3.05</v>
@@ -2996,38 +2996,38 @@
         <v>12700</v>
       </c>
       <c r="M28" t="n">
-        <v>9790</v>
+        <v>9720</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>137185909210</v>
+        <v>138547283810</v>
       </c>
       <c r="P28" t="n">
         <v>12700</v>
       </c>
       <c r="Q28" t="n">
-        <v>9790</v>
+        <v>9720</v>
       </c>
       <c r="R28" t="n">
         <v>-41000</v>
       </c>
       <c r="S28" t="n">
-        <v>-259000</v>
+        <v>-265000</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>높은 영업이익(216억) 및 매출(1042억)을 기반으로 인텔리빅스와 비교하며 알짜배기 기업으로 평가. 주포의 움직임 및 손바뀜 이후 상승 기대.</t>
+          <t>상장 후 급락, 주관사 사기 의혹 제기. 높은 영업이익 대비 주가 부진.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['영업이익', '매출', '손바뀜']</t>
+          <t>['영업이익', '상장', '주가']</t>
         </is>
       </c>
       <c r="X28" t="n">

--- a/data/trending_integrated_20261030_14.xlsx
+++ b/data/trending_integrated_20261030_14.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24050</v>
+        <v>23550</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+167.22%</t>
+          <t>'+161.67%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G2" t="n">
-        <v>757</v>
+        <v>772</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>820316737265</v>
+        <v>827747792665</v>
       </c>
       <c r="P2" t="n">
         <v>27100</v>
@@ -619,23 +619,23 @@
         <v>16450</v>
       </c>
       <c r="R2" t="n">
-        <v>-174000</v>
+        <v>-180000</v>
       </c>
       <c r="S2" t="n">
         <v>-88000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 관련주로 정부 지원 기대감 속 급등락 반복. 투자 주의 및 관망 의견.</t>
+          <t>AI 관련 정부 지원 및 26년 IPO 대장 기대감. 단기 급등 후 급락 패턴 분석. 개인 투자자 단타 위험성 경고. 품절주 특성 및 3파동 시작 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', 'IPO', '패턴']</t>
+          <t>['AI', 'IPO', '품절주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7650</v>
+        <v>7510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.60%</t>
+          <t>'+20.35%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F3" t="n">
         <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>37084301485</v>
+        <v>38119186750</v>
       </c>
       <c r="P3" t="n">
         <v>16620</v>
@@ -711,14 +711,14 @@
         <v>4600</v>
       </c>
       <c r="R3" t="n">
-        <v>-1000</v>
+        <v>3000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>건설업 경기 회복 기대감 속 주가 상승 시도. 유증 성공 및 주가 조작 의혹.</t>
+          <t>급등 및 연상 기대감. 논현동, 천일고속, 동양건설 등 건설사 언급. 유증 성공 가능성 및 주포의 단기 시세 조종 의혹. 건설 산업 활성화에 따른 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['건설', '유증', '주포']</t>
+          <t>['급등', '유증', '주포']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19500</v>
+        <v>19780</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.12%</t>
+          <t>'+18.80%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F4" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G4" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -794,7 +794,7 @@
         <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>133277366325</v>
+        <v>135396561430</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -803,23 +803,23 @@
         <v>6320</v>
       </c>
       <c r="R4" t="n">
-        <v>67000</v>
+        <v>69000</v>
       </c>
       <c r="S4" t="n">
         <v>28000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 양자 보안 의무화 및 바이낸스, 빗썸 해킹 사태로 인한 최대 수혜주 부각. 기술력 및 수혜 전망.</t>
+          <t>정부 양자 보안 의무화 및 해킹 사태 수혜주 부각. 기술력 및 신원 인증 중요성 강조. SGA솔루션즈 상한가 영향. 보안주 섹터 전반의 전망. 프로그램 매수세 및 계단식 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자보안', '해킹', '수혜주']</t>
+          <t>['양자 보안', '해킹', '수혜주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8840</v>
+        <v>8960</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.81%</t>
+          <t>'+16.36%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.37</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H5" t="n">
         <v>13.29</v>
@@ -886,7 +886,7 @@
         <v>12.92</v>
       </c>
       <c r="O5" t="n">
-        <v>9363482855</v>
+        <v>10667645350</v>
       </c>
       <c r="P5" t="n">
         <v>13670</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2810</v>
+        <v>2800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+14.69%</t>
+          <t>'+14.29%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -978,7 +978,7 @@
         <v>0.63</v>
       </c>
       <c r="O6" t="n">
-        <v>12930487922</v>
+        <v>13008689332</v>
       </c>
       <c r="P6" t="n">
         <v>3170</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11840</v>
+        <v>11860</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.71%</t>
+          <t>'+5.89%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="F7" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G7" t="n">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="H7" t="n">
         <v>15.04</v>
@@ -1070,7 +1070,7 @@
         <v>15.08</v>
       </c>
       <c r="O7" t="n">
-        <v>59006481950</v>
+        <v>59294548625</v>
       </c>
       <c r="P7" t="n">
         <v>18960</v>
@@ -1079,23 +1079,23 @@
         <v>5730</v>
       </c>
       <c r="R7" t="n">
-        <v>-396000</v>
+        <v>-423000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색 LED 개발 성공 및 100억 달러 시장 석권 전망. 기술력 기반 주가 우상향 기대.</t>
+          <t>세계 1위 희토류 없는 백색 LED 개발 및 기술력 강조. 100억 달러 시장 석권 기대. 공매도 제도 폐지 요구. 주당 10만원 이상 정상 가격 제시. 반등 및 우상향 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['백색LED', '희토류', '기술개발']</t>
+          <t>['백색 LED', '희토류', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1136,7 +1136,7 @@
         <v>67</v>
       </c>
       <c r="G8" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H8" t="n">
         <v>23.82</v>
@@ -1162,7 +1162,7 @@
         <v>24.64</v>
       </c>
       <c r="O8" t="n">
-        <v>68325986450</v>
+        <v>69331707100</v>
       </c>
       <c r="P8" t="n">
         <v>97900</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15690</v>
+        <v>15780</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.74%</t>
+          <t>'+5.34%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>59</v>
       </c>
       <c r="G9" t="n">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="H9" t="n">
         <v>7.15</v>
@@ -1254,7 +1254,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>54967663705</v>
+        <v>55724970015</v>
       </c>
       <c r="P9" t="n">
         <v>49800</v>
@@ -1314,13 +1314,13 @@
         <v>-0.36</v>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="H10" t="n">
         <v>4.69</v>
@@ -1346,7 +1346,7 @@
         <v>5.05</v>
       </c>
       <c r="O10" t="n">
-        <v>126330952775</v>
+        <v>127364695025</v>
       </c>
       <c r="P10" t="n">
         <v>50600</v>
@@ -1391,184 +1391,184 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4045</v>
+        <v>15750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.77</v>
+        <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="G11" t="n">
-        <v>209</v>
+        <v>353</v>
       </c>
       <c r="H11" t="n">
-        <v>1.43</v>
+        <v>28.13</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>4040</v>
+        <v>15720</v>
       </c>
       <c r="K11" t="n">
-        <v>3925</v>
+        <v>15420</v>
       </c>
       <c r="L11" t="n">
-        <v>4265</v>
+        <v>16050</v>
       </c>
       <c r="M11" t="n">
-        <v>3880</v>
+        <v>15320</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>82572158540</v>
+        <v>55828335805</v>
       </c>
       <c r="P11" t="n">
-        <v>8100</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>592</v>
+        <v>15320</v>
       </c>
       <c r="R11" t="n">
-        <v>78000</v>
+        <v>788000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-71000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국내 시장 폭락 속에서도 견조한 흐름 보이는 빛과전자. 50층 돌파 및 6천원 도달 기대감. 외국인, 프로그램 매수세 관찰.</t>
+          <t>3분기 실적 서프라이즈 및 미국 조선주 강세 속 국내 조선주 약세 진단. 정기선 승계와 증여세 상관관계 의문 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['상승', '기대감', '외국인매수']</t>
+          <t>['실적', '조선주', '승계']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15715</v>
+        <v>4025</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.03%</t>
+          <t>'-0.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="F12" t="n">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="G12" t="n">
-        <v>351</v>
+        <v>216</v>
       </c>
       <c r="H12" t="n">
-        <v>28.13</v>
+        <v>1.43</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>15720</v>
+        <v>4040</v>
       </c>
       <c r="K12" t="n">
-        <v>15420</v>
+        <v>3925</v>
       </c>
       <c r="L12" t="n">
-        <v>16050</v>
+        <v>4265</v>
       </c>
       <c r="M12" t="n">
-        <v>15320</v>
+        <v>3880</v>
       </c>
       <c r="N12" t="n">
-        <v>28.07</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>54274481330</v>
+        <v>82849722139</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>8100</v>
       </c>
       <c r="Q12" t="n">
-        <v>15320</v>
+        <v>592</v>
       </c>
       <c r="R12" t="n">
-        <v>788000</v>
+        <v>55000</v>
       </c>
       <c r="S12" t="n">
-        <v>-71000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3분기 실적 서프라이즈 및 미국 조선주 강세 속 국내 조선주 약세 진단. 정기선 승계와 증여세 상관관계 의문 제기.</t>
+          <t>국내 시장 폭락 속에서도 견조한 흐름 보이는 빛과전자. 50층 돌파 및 6천원 도달 기대감. 외국인, 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적', '조선주', '승계']</t>
+          <t>['상승', '기대감', '외국인매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7280</v>
+        <v>7290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.28%</t>
+          <t>'-2.15%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
         <v>30</v>
       </c>
       <c r="G13" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="H13" t="n">
         <v>25.3</v>
@@ -1622,7 +1622,7 @@
         <v>25.32</v>
       </c>
       <c r="O13" t="n">
-        <v>10732249525</v>
+        <v>11134948990</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>61300</v>
+        <v>225000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.39%</t>
+          <t>'-3.02%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.21</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>78</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>504</v>
       </c>
       <c r="G14" t="n">
-        <v>372</v>
+        <v>1190</v>
       </c>
       <c r="H14" t="n">
-        <v>41.76</v>
+        <v>46.17</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>62800</v>
+        <v>232000</v>
       </c>
       <c r="K14" t="n">
-        <v>62300</v>
+        <v>223500</v>
       </c>
       <c r="L14" t="n">
-        <v>62800</v>
+        <v>229500</v>
       </c>
       <c r="M14" t="n">
-        <v>60700</v>
+        <v>216500</v>
       </c>
       <c r="N14" t="n">
-        <v>41.55</v>
+        <v>46.19</v>
       </c>
       <c r="O14" t="n">
-        <v>99578355250</v>
+        <v>3159280815250</v>
       </c>
       <c r="P14" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R14" t="n">
-        <v>-65000</v>
+        <v>538000</v>
       </c>
       <c r="S14" t="n">
-        <v>-81000</v>
+        <v>241000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
+          <t>이재용 경영 퇴진 및 자사주 매입/소각 요구. 일론 머스크 비교 및 주가 하락 책임론 제기. 정치적 비난 및 좌파 정권 비판. 주가 부양 의지 부족 지적.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,90 +1739,90 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
+          <t>['자사주 매입', '소각', '주가 조작']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8310</v>
+        <v>60900</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.15%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="E15" t="n">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="F15" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="G15" t="n">
-        <v>300</v>
+        <v>392</v>
       </c>
       <c r="H15" t="n">
-        <v>2.67</v>
+        <v>41.76</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8580</v>
+        <v>62800</v>
       </c>
       <c r="K15" t="n">
-        <v>11090</v>
+        <v>62300</v>
       </c>
       <c r="L15" t="n">
-        <v>11150</v>
+        <v>62800</v>
       </c>
       <c r="M15" t="n">
-        <v>8070</v>
+        <v>60700</v>
       </c>
       <c r="N15" t="n">
-        <v>2.66</v>
+        <v>41.55</v>
       </c>
       <c r="O15" t="n">
-        <v>30200342665</v>
+        <v>102295149350</v>
       </c>
       <c r="P15" t="n">
-        <v>19270</v>
+        <v>67300</v>
       </c>
       <c r="Q15" t="n">
-        <v>2135</v>
+        <v>23150</v>
       </c>
       <c r="R15" t="n">
-        <v>-396000</v>
+        <v>-65000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-81000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>서울바이오시스의 독점 기술 및 신규 기술(광통신, 와이캅3)에 대한 기대감 존재. 환기 문제 해소 및 외인 유입 가능성 언급.</t>
+          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광반도체', '와이캅3', '환기']</t>
+          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,99 +1844,99 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>224500</v>
+        <v>8300</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.23%</t>
+          <t>'-3.26%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>117</v>
       </c>
       <c r="F16" t="n">
-        <v>506</v>
+        <v>66</v>
       </c>
       <c r="G16" t="n">
-        <v>1266</v>
+        <v>308</v>
       </c>
       <c r="H16" t="n">
-        <v>46.17</v>
+        <v>2.67</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>232000</v>
+        <v>8580</v>
       </c>
       <c r="K16" t="n">
-        <v>223500</v>
+        <v>11090</v>
       </c>
       <c r="L16" t="n">
-        <v>229500</v>
+        <v>11150</v>
       </c>
       <c r="M16" t="n">
-        <v>216500</v>
+        <v>8070</v>
       </c>
       <c r="N16" t="n">
-        <v>46.19</v>
+        <v>2.66</v>
       </c>
       <c r="O16" t="n">
-        <v>3075451193250</v>
+        <v>30262911685</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>19270</v>
       </c>
       <c r="Q16" t="n">
-        <v>94500</v>
+        <v>2135</v>
       </c>
       <c r="R16" t="n">
-        <v>538000</v>
+        <v>-396000</v>
       </c>
       <c r="S16" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>이재용 경영 퇴진, 자사주 매입 소각 촉구. 정치적 이슈와 연계된 주가 부양 압박.</t>
+          <t>서울바이오시스의 독점 기술 및 신규 기술(광통신, 와이캅3)에 대한 기대감 존재. 환기 문제 해소 및 외인 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['이재용', '상속세', '자사주']</t>
+          <t>['광반도체', '와이캅3', '환기']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
@@ -1947,18 +1947,18 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6400</v>
+        <v>6340</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-4.52%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F17" t="n">
         <v>38</v>
@@ -1990,7 +1990,7 @@
         <v>0.9</v>
       </c>
       <c r="O17" t="n">
-        <v>32201335060</v>
+        <v>32250787130</v>
       </c>
       <c r="P17" t="n">
         <v>9820</v>
@@ -1999,7 +1999,7 @@
         <v>4000</v>
       </c>
       <c r="R17" t="n">
-        <v>-55000</v>
+        <v>-27000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22600</v>
+        <v>175000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.24%</t>
+          <t>'-4.84%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.63</v>
+        <v>-0.13</v>
       </c>
       <c r="E18" t="n">
-        <v>272</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
-        <v>175</v>
+        <v>55</v>
       </c>
       <c r="G18" t="n">
-        <v>639</v>
+        <v>262</v>
       </c>
       <c r="H18" t="n">
-        <v>11.6</v>
+        <v>74.87</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,91 +2067,91 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>23600</v>
+        <v>183900</v>
       </c>
       <c r="K18" t="n">
-        <v>22650</v>
+        <v>176800</v>
       </c>
       <c r="L18" t="n">
-        <v>22750</v>
+        <v>179000</v>
       </c>
       <c r="M18" t="n">
-        <v>21100</v>
+        <v>168100</v>
       </c>
       <c r="N18" t="n">
-        <v>12.23</v>
+        <v>75</v>
       </c>
       <c r="O18" t="n">
-        <v>90360433675</v>
+        <v>670871545500</v>
       </c>
       <c r="P18" t="n">
-        <v>59300</v>
+        <v>243500</v>
       </c>
       <c r="Q18" t="n">
-        <v>21100</v>
+        <v>71000</v>
       </c>
       <c r="R18" t="n">
-        <v>-728000</v>
+        <v>-802000</v>
       </c>
       <c r="S18" t="n">
-        <v>-220000</v>
+        <v>15000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>한화솔루션의 주가 급락에 대한 의혹 제기. RE100 승인 및 카터스빌 물량 완판 소식에도 불구하고 주가 부진. 실적 턴어라운드에도 불구하고 주가 하락.</t>
+          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 누르기', 'RE100', '실적 턴어라운드']</t>
+          <t>['주가 조작', '증여세', '우선주 소각']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>175200</v>
+        <v>22450</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.73%</t>
+          <t>'-4.87%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.13</v>
+        <v>-0.63</v>
       </c>
       <c r="E19" t="n">
-        <v>68</v>
+        <v>272</v>
       </c>
       <c r="F19" t="n">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="G19" t="n">
-        <v>258</v>
+        <v>639</v>
       </c>
       <c r="H19" t="n">
-        <v>74.87</v>
+        <v>11.6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,60 +2159,60 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>183900</v>
+        <v>23600</v>
       </c>
       <c r="K19" t="n">
-        <v>176800</v>
+        <v>22650</v>
       </c>
       <c r="L19" t="n">
-        <v>179000</v>
+        <v>22750</v>
       </c>
       <c r="M19" t="n">
-        <v>168100</v>
+        <v>21100</v>
       </c>
       <c r="N19" t="n">
-        <v>75</v>
+        <v>12.23</v>
       </c>
       <c r="O19" t="n">
-        <v>656836494450</v>
+        <v>92060778750</v>
       </c>
       <c r="P19" t="n">
-        <v>243500</v>
+        <v>59300</v>
       </c>
       <c r="Q19" t="n">
-        <v>71000</v>
+        <v>21100</v>
       </c>
       <c r="R19" t="n">
-        <v>-802000</v>
+        <v>-728000</v>
       </c>
       <c r="S19" t="n">
-        <v>15000</v>
+        <v>-220000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
+          <t>한화솔루션의 주가 급락에 대한 의혹 제기. RE100 승인 및 카터스빌 물량 완판 소식에도 불구하고 주가 부진. 실적 턴어라운드에도 불구하고 주가 하락.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주가 조작', '증여세', '우선주 소각']</t>
+          <t>['주가 누르기', 'RE100', '실적 턴어라운드']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
@@ -2234,13 +2234,13 @@
         <v>-0.2</v>
       </c>
       <c r="E20" t="n">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F20" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="G20" t="n">
-        <v>1168</v>
+        <v>1187</v>
       </c>
       <c r="H20" t="n">
         <v>22.14</v>
@@ -2266,7 +2266,7 @@
         <v>22.34</v>
       </c>
       <c r="O20" t="n">
-        <v>92299365650</v>
+        <v>93279874350</v>
       </c>
       <c r="P20" t="n">
         <v>139200</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11000</v>
+        <v>10950</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.34%</t>
+          <t>'-5.77%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="F21" t="n">
         <v>184</v>
       </c>
       <c r="G21" t="n">
-        <v>1363</v>
+        <v>1397</v>
       </c>
       <c r="H21" t="n">
         <v>9.73</v>
@@ -2358,7 +2358,7 @@
         <v>9.6</v>
       </c>
       <c r="O21" t="n">
-        <v>59456553295</v>
+        <v>60240337500</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원전 사업 및 가덕도 공사 관련 정부 정책 변화와 공매도 금지 조치가 호재로 해석. 한수원의 갑질 논란과 재건 사업 기회 언급.</t>
+          <t>원전 사업 및 가덕도 공사비 증액 관련 언급. 공매도 금지 조치 영향 분석. 한수원과의 계약 및 재입찰 시점 논의. 러시아, 우크라이나, 중동 재건 사업 전망.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '공매도 금지', '가덕도']</t>
+          <t>['원전', '공사비 증액', '공매도 금지']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1422000</v>
+        <v>1423000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-6.82%</t>
+          <t>'-6.75%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="G22" t="n">
-        <v>1222</v>
+        <v>1195</v>
       </c>
       <c r="H22" t="n">
         <v>48.72</v>
@@ -2450,7 +2450,7 @@
         <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>3694986184500</v>
+        <v>3798476115000</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>샌디스크 역대급 서프라이즈 및 구글, 아마존 AI 투자 확대에 따른 SK하이닉스 실적 기대감. 외인 매수세 유입.</t>
+          <t>주가 반등 및 150 목표가 제시. 샌디스크 실적 호조 및 AI 투자 확대 수혜 기대. 자사주 매수 관련 언급. 외인 매수세 유입 및 개미 털기 분석.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['AI', '샌디스크', '실적']</t>
+          <t>['자사주 매입', 'AI 투자', '외인 매수']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13850</v>
+        <v>13820</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-7.85%</t>
+          <t>'-8.05%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F23" t="n">
         <v>69</v>
       </c>
       <c r="G23" t="n">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>47817418555</v>
+        <v>48358970265</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7110</v>
+        <v>7130</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.00%</t>
+          <t>'-9.75%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F24" t="n">
         <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>16903913275</v>
+        <v>17002110395</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>118000</v>
+        <v>118200</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-14.62%</t>
+          <t>'-14.47%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2700,7 +2700,7 @@
         <v>117</v>
       </c>
       <c r="G25" t="n">
-        <v>570</v>
+        <v>588</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2726,7 +2726,7 @@
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>188499835950</v>
+        <v>191249724700</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>실적 발표 후 주가 급락에 대한 불만 고조. 800억 분기 영업이익에도 불구하고 급락하는 원인에 대한 의문 제기 및 기관 매도세 비판.</t>
+          <t>실적 호조에도 불구하고 주가 급락. 경쟁사 주가 대비 저평가 및 목표가 상향. 개인 투자자 피로감 및 기관 매매 행태 비판. 실적 발표 후 주가 변동성 분석.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['실적', '주가 급락', '기관']</t>
+          <t>['실적', '목표가 상향', '주가 급락']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13890</v>
+        <v>13790</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-18.29%</t>
+          <t>'-18.88%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>67486499370</v>
+        <v>68076680150</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2827,14 +2827,14 @@
         <v>11550</v>
       </c>
       <c r="R26" t="n">
-        <v>57000</v>
+        <v>-16000</v>
       </c>
       <c r="S26" t="n">
         <v>-193000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>보호예수 및 반도체 업황 부진으로 인한 주가 하락에 대한 불만. 독점 기업임에도 힘을 못 쓰는 이유와 급락세에 대한 우려.</t>
+          <t>보호예수 해제 및 시장 개판 상황 언급. 반도체 섹터 부진 영향. 개인 투자자 손실 및 월요일 바닥 매수 전략. 독점 기업으로서의 주가 부진 원인 분석.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체', '주가 하락']</t>
+          <t>['보호예수', '반도체', '독점 기업']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2878,13 +2878,13 @@
         <v>1.45</v>
       </c>
       <c r="E27" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F27" t="n">
         <v>55</v>
       </c>
       <c r="G27" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H27" t="n">
         <v>4.8</v>
@@ -2910,7 +2910,7 @@
         <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>8385265368</v>
+        <v>8419739063</v>
       </c>
       <c r="P27" t="n">
         <v>5700</v>
@@ -2919,14 +2919,14 @@
         <v>1401</v>
       </c>
       <c r="R27" t="n">
-        <v>-30000</v>
+        <v>-43000</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>벡트로보틱스의 하한가 행진에 대한 우려. 납입 관련 이슈 및 상장폐지 가능성 제기. 대규모 하락 및 개인 투자자 손실 예상.</t>
+          <t>자금 납입 및 공시 관련 불확실성 속 하한가 하락 및 상폐 우려, 일부 매수세 유입 관찰.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['하한가', '납입', '상장폐지']</t>
+          <t>['하한가', '공시', '상폐']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9730</v>
+        <v>9720</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-35.13%</t>
+          <t>'-35.20%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="F28" t="n">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="G28" t="n">
-        <v>897</v>
+        <v>920</v>
       </c>
       <c r="H28" t="n">
         <v>3.05</v>
@@ -2996,19 +2996,19 @@
         <v>12700</v>
       </c>
       <c r="M28" t="n">
-        <v>9720</v>
+        <v>9620</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>138547283810</v>
+        <v>140196421725</v>
       </c>
       <c r="P28" t="n">
         <v>12700</v>
       </c>
       <c r="Q28" t="n">
-        <v>9720</v>
+        <v>9620</v>
       </c>
       <c r="R28" t="n">
         <v>-41000</v>
@@ -3018,16 +3018,16 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>상장 후 급락, 주관사 사기 의혹 제기. 높은 영업이익 대비 주가 부진.</t>
+          <t>상장 후 주가 급락 및 상장 주관사 사기 의혹 제기. 높은 영업이익 대비 주가 부진. 인텔리빅스와의 비교 및 크리에이츠의 알짜배기 속성 강조. 실내 골프 대중화 전망.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['영업이익', '상장', '주가']</t>
+          <t>['영업이익', '주가 부진', '실내 골프']</t>
         </is>
       </c>
       <c r="X28" t="n">

--- a/data/trending_integrated_20261030_14.xlsx
+++ b/data/trending_integrated_20261030_14.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23550</v>
+        <v>25650</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+161.67%</t>
+          <t>'+185.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G2" t="n">
-        <v>772</v>
+        <v>792</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>827747792665</v>
+        <v>853207375015</v>
       </c>
       <c r="P2" t="n">
         <v>27100</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 관련 정부 지원 및 26년 IPO 대장 기대감. 단기 급등 후 급락 패턴 분석. 개인 투자자 단타 위험성 경고. 품절주 특성 및 3파동 시작 가능성 언급.</t>
+          <t>AI 관련 정부 지원 기대감 및 26년 IPO 대장 전망 언급. 13년 연속 흑자 기업으로 저평가 가능성 제기. 그러나 급락 패턴 반복 지적.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', 'IPO', '품절주']</t>
+          <t>['AI', 'IPO', '흑자']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7510</v>
+        <v>7320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.35%</t>
+          <t>'+17.31%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F3" t="n">
         <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>38119186750</v>
+        <v>38573317930</v>
       </c>
       <c r="P3" t="n">
         <v>16620</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19780</v>
+        <v>19450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+18.80%</t>
+          <t>'+16.82%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,7 +765,7 @@
         <v>161</v>
       </c>
       <c r="F4" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G4" t="n">
         <v>214</v>
@@ -794,7 +794,7 @@
         <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>135396561430</v>
+        <v>136935149460</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8960</v>
+        <v>8830</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+16.36%</t>
+          <t>'+14.68%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H5" t="n">
         <v>13.29</v>
@@ -886,7 +886,7 @@
         <v>12.92</v>
       </c>
       <c r="O5" t="n">
-        <v>10667645350</v>
+        <v>10877469130</v>
       </c>
       <c r="P5" t="n">
         <v>13670</v>
@@ -946,10 +946,10 @@
         <v>0.16</v>
       </c>
       <c r="E6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>37</v>
@@ -978,7 +978,7 @@
         <v>0.63</v>
       </c>
       <c r="O6" t="n">
-        <v>13008689332</v>
+        <v>13059988571</v>
       </c>
       <c r="P6" t="n">
         <v>3170</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>서울반도체</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11860</v>
+        <v>15810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.89%</t>
+          <t>'+5.54%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.04</v>
+        <v>-0.9</v>
       </c>
       <c r="E7" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="F7" t="n">
-        <v>202</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>988</v>
+        <v>422</v>
       </c>
       <c r="H7" t="n">
-        <v>15.04</v>
+        <v>7.15</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,60 +1055,60 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11200</v>
+        <v>14980</v>
       </c>
       <c r="K7" t="n">
-        <v>13500</v>
+        <v>14980</v>
       </c>
       <c r="L7" t="n">
-        <v>13710</v>
+        <v>16150</v>
       </c>
       <c r="M7" t="n">
-        <v>11620</v>
+        <v>14610</v>
       </c>
       <c r="N7" t="n">
-        <v>15.08</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>59294548625</v>
+        <v>56406361710</v>
       </c>
       <c r="P7" t="n">
-        <v>18960</v>
+        <v>49800</v>
       </c>
       <c r="Q7" t="n">
-        <v>5730</v>
+        <v>8180</v>
       </c>
       <c r="R7" t="n">
-        <v>-423000</v>
+        <v>84000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>179000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>세계 1위 희토류 없는 백색 LED 개발 및 기술력 강조. 100억 달러 시장 석권 기대. 공매도 제도 폐지 요구. 주당 10만원 이상 정상 가격 제시. 반등 및 우상향 전망.</t>
+          <t>루닛의 FDA 승인 신청 및 미국 보험 등재 기대감. 유방암 위험 예측 솔루션의 시장 확대 전망. 공매도 압력에도 불구하고 주가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['백색 LED', '희토류', '공매도']</t>
+          <t>['FDA 승인', '유방암', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>046890</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51800</v>
+        <v>51600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.50%</t>
+          <t>'+5.09%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.82</v>
       </c>
       <c r="E8" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G8" t="n">
         <v>255</v>
@@ -1162,7 +1162,7 @@
         <v>24.64</v>
       </c>
       <c r="O8" t="n">
-        <v>69331707100</v>
+        <v>70048042900</v>
       </c>
       <c r="P8" t="n">
         <v>97900</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>역대 최대 실적 발표에도 불구하고 주가가 지지부진한 상황에 대한 불만과 함께, 공매도 세력과의 공방 속 상승 기대감이 있음.</t>
+          <t>TC본더 매출 본격화 및 공매도 타격 전망. 사상 최대 실적 발표 기반 하락 후 반등 기대. 한미반도체와 비교하며 저평가 주장.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['실적', '공매도', 'TC본더']</t>
+          <t>['TC본더', '실적', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>서울반도체</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15780</v>
+        <v>11760</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.34%</t>
+          <t>'+5.00%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.9</v>
+        <v>-0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>353</v>
       </c>
       <c r="F9" t="n">
-        <v>59</v>
+        <v>202</v>
       </c>
       <c r="G9" t="n">
-        <v>418</v>
+        <v>1009</v>
       </c>
       <c r="H9" t="n">
-        <v>7.15</v>
+        <v>15.04</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,60 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14980</v>
+        <v>11200</v>
       </c>
       <c r="K9" t="n">
-        <v>14980</v>
+        <v>13500</v>
       </c>
       <c r="L9" t="n">
-        <v>16150</v>
+        <v>13710</v>
       </c>
       <c r="M9" t="n">
-        <v>14610</v>
+        <v>11620</v>
       </c>
       <c r="N9" t="n">
-        <v>8.050000000000001</v>
+        <v>15.08</v>
       </c>
       <c r="O9" t="n">
-        <v>55724970015</v>
+        <v>59930801310</v>
       </c>
       <c r="P9" t="n">
-        <v>49800</v>
+        <v>18960</v>
       </c>
       <c r="Q9" t="n">
-        <v>8180</v>
+        <v>5730</v>
       </c>
       <c r="R9" t="n">
-        <v>84000</v>
+        <v>-423000</v>
       </c>
       <c r="S9" t="n">
-        <v>179000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>루닛의 FDA 승인 신청 및 미국 보험 등재 기대감. 유방암 위험 예측 솔루션의 시장 확대 전망. 공매도 압력에도 불구하고 주가 상승 가능성 언급.</t>
+          <t>세계 1위 희토류 없는 백색 LED 개발 및 기술력 강조. 100억 달러 시장 석권 기대. 공매도 제도 폐지 요구. 주당 10만원 이상 정상 가격 제시. 반등 및 우상향 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA 승인', '유방암', '공매도']</t>
+          <t>['백색 LED', '희토류', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>046890</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29050</v>
+        <v>29000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.57%</t>
+          <t>'+3.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.36</v>
       </c>
       <c r="E10" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F10" t="n">
         <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="H10" t="n">
         <v>4.69</v>
@@ -1346,7 +1346,7 @@
         <v>5.05</v>
       </c>
       <c r="O10" t="n">
-        <v>127364695025</v>
+        <v>127917470525</v>
       </c>
       <c r="P10" t="n">
         <v>50600</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15750</v>
+        <v>15730</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.19%</t>
+          <t>'+0.06%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F11" t="n">
         <v>71</v>
       </c>
       <c r="G11" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H11" t="n">
         <v>28.13</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>55828335805</v>
+        <v>57483838265</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4025</v>
+        <v>4005</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.37%</t>
+          <t>'-0.87%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
         <v>216</v>
@@ -1530,7 +1530,7 @@
         <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>82849722139</v>
+        <v>83209405871</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7290</v>
+        <v>7280</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.15%</t>
+          <t>'-2.28%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>30</v>
       </c>
       <c r="G13" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="H13" t="n">
         <v>25.3</v>
@@ -1622,7 +1622,7 @@
         <v>25.32</v>
       </c>
       <c r="O13" t="n">
-        <v>11134948990</v>
+        <v>11297715840</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>225000</v>
+        <v>60900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.02%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>84</v>
       </c>
       <c r="F14" t="n">
-        <v>504</v>
+        <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>1190</v>
+        <v>402</v>
       </c>
       <c r="H14" t="n">
-        <v>46.17</v>
+        <v>41.76</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>232000</v>
+        <v>62800</v>
       </c>
       <c r="K14" t="n">
-        <v>223500</v>
+        <v>62300</v>
       </c>
       <c r="L14" t="n">
-        <v>229500</v>
+        <v>62800</v>
       </c>
       <c r="M14" t="n">
-        <v>216500</v>
+        <v>60500</v>
       </c>
       <c r="N14" t="n">
-        <v>46.19</v>
+        <v>41.55</v>
       </c>
       <c r="O14" t="n">
-        <v>3159280815250</v>
+        <v>104966693450</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q14" t="n">
-        <v>94500</v>
+        <v>23150</v>
       </c>
       <c r="R14" t="n">
-        <v>538000</v>
+        <v>-65000</v>
       </c>
       <c r="S14" t="n">
-        <v>241000</v>
+        <v>-81000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>이재용 경영 퇴진 및 자사주 매입/소각 요구. 일론 머스크 비교 및 주가 하락 책임론 제기. 정치적 비난 및 좌파 정권 비판. 주가 부양 의지 부족 지적.</t>
+          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,90 +1739,90 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주 매입', '소각', '주가 조작']</t>
+          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60900</v>
+        <v>6370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.03%</t>
+          <t>'-4.07%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="E15" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
-        <v>392</v>
+        <v>86</v>
       </c>
       <c r="H15" t="n">
-        <v>41.76</v>
+        <v>0.85</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>62800</v>
+        <v>6640</v>
       </c>
       <c r="K15" t="n">
-        <v>62300</v>
+        <v>7210</v>
       </c>
       <c r="L15" t="n">
-        <v>62800</v>
+        <v>7500</v>
       </c>
       <c r="M15" t="n">
-        <v>60700</v>
+        <v>6230</v>
       </c>
       <c r="N15" t="n">
-        <v>41.55</v>
+        <v>0.9</v>
       </c>
       <c r="O15" t="n">
-        <v>102295149350</v>
+        <v>32334016890</v>
       </c>
       <c r="P15" t="n">
-        <v>67300</v>
+        <v>9820</v>
       </c>
       <c r="Q15" t="n">
-        <v>23150</v>
+        <v>4000</v>
       </c>
       <c r="R15" t="n">
-        <v>-65000</v>
+        <v>-27000</v>
       </c>
       <c r="S15" t="n">
-        <v>-81000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,130 +1844,130 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8300</v>
+        <v>222500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.26%</t>
+          <t>'-4.09%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>117</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>66</v>
+        <v>498</v>
       </c>
       <c r="G16" t="n">
-        <v>308</v>
+        <v>1138</v>
       </c>
       <c r="H16" t="n">
-        <v>2.67</v>
+        <v>46.17</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8580</v>
+        <v>232000</v>
       </c>
       <c r="K16" t="n">
-        <v>11090</v>
+        <v>223500</v>
       </c>
       <c r="L16" t="n">
-        <v>11150</v>
+        <v>229500</v>
       </c>
       <c r="M16" t="n">
-        <v>8070</v>
+        <v>216500</v>
       </c>
       <c r="N16" t="n">
-        <v>2.66</v>
+        <v>46.19</v>
       </c>
       <c r="O16" t="n">
-        <v>30262911685</v>
+        <v>3210313834000</v>
       </c>
       <c r="P16" t="n">
-        <v>19270</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>2135</v>
+        <v>94500</v>
       </c>
       <c r="R16" t="n">
-        <v>-396000</v>
+        <v>538000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>서울바이오시스의 독점 기술 및 신규 기술(광통신, 와이캅3)에 대한 기대감 존재. 환기 문제 해소 및 외인 유입 가능성 언급.</t>
+          <t>이재용 경영 퇴출 및 자사주 매입/소각 요구. 일론 머스크와 비교하며 시총 상승 기대 언급. 정치적 발언 다수.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광반도체', '와이캅3', '환기']</t>
+          <t>['자사주', '이재용', '시총']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6340</v>
+        <v>8210</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.52%</t>
+          <t>'-4.31%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="G17" t="n">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="H17" t="n">
-        <v>0.85</v>
+        <v>2.67</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6640</v>
+        <v>8580</v>
       </c>
       <c r="K17" t="n">
-        <v>7210</v>
+        <v>11090</v>
       </c>
       <c r="L17" t="n">
-        <v>7500</v>
+        <v>11150</v>
       </c>
       <c r="M17" t="n">
-        <v>6230</v>
+        <v>8070</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9</v>
+        <v>2.66</v>
       </c>
       <c r="O17" t="n">
-        <v>32250787130</v>
+        <v>30336950410</v>
       </c>
       <c r="P17" t="n">
-        <v>9820</v>
+        <v>19270</v>
       </c>
       <c r="Q17" t="n">
-        <v>4000</v>
+        <v>2135</v>
       </c>
       <c r="R17" t="n">
-        <v>-27000</v>
+        <v>-396000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>서울바이오시스의 독점 기술 및 신규 기술(광통신, 와이캅3)에 대한 기대감 존재. 환기 문제 해소 및 외인 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['광반도체', '와이캅3', '환기']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>175000</v>
+        <v>22450</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.84%</t>
+          <t>'-4.87%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.13</v>
+        <v>-0.63</v>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>273</v>
       </c>
       <c r="F18" t="n">
-        <v>55</v>
+        <v>177</v>
       </c>
       <c r="G18" t="n">
-        <v>262</v>
+        <v>647</v>
       </c>
       <c r="H18" t="n">
-        <v>74.87</v>
+        <v>11.6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,91 +2067,91 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>183900</v>
+        <v>23600</v>
       </c>
       <c r="K18" t="n">
-        <v>176800</v>
+        <v>22650</v>
       </c>
       <c r="L18" t="n">
-        <v>179000</v>
+        <v>22750</v>
       </c>
       <c r="M18" t="n">
-        <v>168100</v>
+        <v>21100</v>
       </c>
       <c r="N18" t="n">
-        <v>75</v>
+        <v>12.23</v>
       </c>
       <c r="O18" t="n">
-        <v>670871545500</v>
+        <v>93300076475</v>
       </c>
       <c r="P18" t="n">
-        <v>243500</v>
+        <v>59300</v>
       </c>
       <c r="Q18" t="n">
-        <v>71000</v>
+        <v>21100</v>
       </c>
       <c r="R18" t="n">
-        <v>-802000</v>
+        <v>-728000</v>
       </c>
       <c r="S18" t="n">
-        <v>15000</v>
+        <v>-220000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
+          <t>한화솔루션의 주가 급락에 대한 의혹 제기. RE100 승인 및 카터스빌 물량 완판 소식에도 불구하고 주가 부진. 실적 턴어라운드에도 불구하고 주가 하락.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 조작', '증여세', '우선주 소각']</t>
+          <t>['주가 누르기', 'RE100', '실적 턴어라운드']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22450</v>
+        <v>53800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.87%</t>
+          <t>'-5.11%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.63</v>
+        <v>-0.2</v>
       </c>
       <c r="E19" t="n">
-        <v>272</v>
+        <v>370</v>
       </c>
       <c r="F19" t="n">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="G19" t="n">
-        <v>639</v>
+        <v>1218</v>
       </c>
       <c r="H19" t="n">
-        <v>11.6</v>
+        <v>22.14</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>23600</v>
+        <v>56700</v>
       </c>
       <c r="K19" t="n">
-        <v>22650</v>
+        <v>55500</v>
       </c>
       <c r="L19" t="n">
-        <v>22750</v>
+        <v>55900</v>
       </c>
       <c r="M19" t="n">
-        <v>21100</v>
+        <v>53700</v>
       </c>
       <c r="N19" t="n">
-        <v>12.23</v>
+        <v>22.34</v>
       </c>
       <c r="O19" t="n">
-        <v>92060778750</v>
+        <v>95393615550</v>
       </c>
       <c r="P19" t="n">
-        <v>59300</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>21100</v>
+        <v>53400</v>
       </c>
       <c r="R19" t="n">
-        <v>-728000</v>
+        <v>-281000</v>
       </c>
       <c r="S19" t="n">
-        <v>-220000</v>
+        <v>-89000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>한화솔루션의 주가 급락에 대한 의혹 제기. RE100 승인 및 카터스빌 물량 완판 소식에도 불구하고 주가 부진. 실적 턴어라운드에도 불구하고 주가 하락.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 관련 긍정적 언급. 다만, 정부 정책 및 시장 상황에 대한 부정적 평가가 sentiment에 영향을 미치며 fact score는 구체적인 수주 내용을 기반으로 산정.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주가 누르기', 'RE100', '실적 턴어라운드']</t>
+          <t>['SMR', '원자로 수주', '실적']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>53900</v>
+        <v>173400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.94%</t>
+          <t>'-5.71%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>365</v>
+        <v>70</v>
       </c>
       <c r="F20" t="n">
-        <v>237</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>1187</v>
+        <v>243</v>
       </c>
       <c r="H20" t="n">
-        <v>22.14</v>
+        <v>74.87</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,60 +2251,60 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>56700</v>
+        <v>183900</v>
       </c>
       <c r="K20" t="n">
-        <v>55500</v>
+        <v>176800</v>
       </c>
       <c r="L20" t="n">
-        <v>55900</v>
+        <v>179000</v>
       </c>
       <c r="M20" t="n">
-        <v>53700</v>
+        <v>168100</v>
       </c>
       <c r="N20" t="n">
-        <v>22.34</v>
+        <v>75</v>
       </c>
       <c r="O20" t="n">
-        <v>93279874350</v>
+        <v>683994853500</v>
       </c>
       <c r="P20" t="n">
-        <v>139200</v>
+        <v>243500</v>
       </c>
       <c r="Q20" t="n">
-        <v>53400</v>
+        <v>71000</v>
       </c>
       <c r="R20" t="n">
-        <v>-281000</v>
+        <v>-802000</v>
       </c>
       <c r="S20" t="n">
-        <v>-89000</v>
+        <v>15000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 관련 긍정적 언급. 다만, 정부 정책 및 시장 상황에 대한 부정적 평가가 sentiment에 영향을 미치며 fact score는 구체적인 수주 내용을 기반으로 산정.</t>
+          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['SMR', '원자로 수주', '실적']</t>
+          <t>['주가 조작', '증여세', '우선주 소각']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10950</v>
+        <v>10910</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.77%</t>
+          <t>'-6.11%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="F21" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G21" t="n">
-        <v>1397</v>
+        <v>1417</v>
       </c>
       <c r="H21" t="n">
         <v>9.73</v>
@@ -2352,13 +2352,13 @@
         <v>11470</v>
       </c>
       <c r="M21" t="n">
-        <v>10890</v>
+        <v>10880</v>
       </c>
       <c r="N21" t="n">
         <v>9.6</v>
       </c>
       <c r="O21" t="n">
-        <v>60240337500</v>
+        <v>61891545970</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1423000</v>
+        <v>1417000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-6.75%</t>
+          <t>'-7.14%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G22" t="n">
-        <v>1195</v>
+        <v>1205</v>
       </c>
       <c r="H22" t="n">
         <v>48.72</v>
@@ -2450,7 +2450,7 @@
         <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>3798476115000</v>
+        <v>3858849720000</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주가 반등 및 150 목표가 제시. 샌디스크 실적 호조 및 AI 투자 확대 수혜 기대. 자사주 매수 관련 언급. 외인 매수세 유입 및 개미 털기 분석.</t>
+          <t>종가 150 기대감 및 반등 가능성 언급. 샌디스크 서프라이즈, AI 투자 확대, 자사주 매입 호재 가능성 제기. 외인 매수세 주목.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['자사주 매입', 'AI 투자', '외인 매수']</t>
+          <t>['자사주', 'AI', '외인']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13820</v>
+        <v>13800</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.05%</t>
+          <t>'-8.18%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F23" t="n">
         <v>69</v>
       </c>
       <c r="G23" t="n">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>48358970265</v>
+        <v>48710948835</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>광케이블 관련 특허 보유 및 호재에도 불구하고 국내 시장 불신으로 인한 주가 하락. 정부 정책 비판.</t>
+          <t>미국 광통신주 강세 및 루닛 사례 언급하며 국내 증시 불신 속 호재 다수 존재 주장. 27년까지 목표가 29000원 제시. 공매도 세력 비판.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['광케이블', '특허', '정부']</t>
+          <t>['광통신', '호재', '공매도']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7130</v>
+        <v>7090</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-9.75%</t>
+          <t>'-10.25%</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>17002110395</v>
+        <v>17121697270</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>118200</v>
+        <v>117400</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-14.47%</t>
+          <t>'-15.05%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F25" t="n">
         <v>117</v>
       </c>
       <c r="G25" t="n">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2726,7 +2726,7 @@
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>191249724700</v>
+        <v>194114335000</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>실적 호조에도 불구하고 주가 급락. 경쟁사 주가 대비 저평가 및 목표가 상향. 개인 투자자 피로감 및 기관 매매 행태 비판. 실적 발표 후 주가 변동성 분석.</t>
+          <t>실적 기반 경쟁사 주가 캐치업 및 목표가 상향 뉴스 인용. 800억 분기 영업이익 언급. 그럼에도 불구하고 급락하는 상황에 대한 의문 제기.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['실적', '목표가 상향', '주가 급락']</t>
+          <t>['실적', '목표가', '영업이익']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13790</v>
+        <v>13620</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-18.88%</t>
+          <t>'-19.88%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>68076680150</v>
+        <v>68952312600</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>보호예수 해제 및 시장 개판 상황 언급. 반도체 섹터 부진 영향. 개인 투자자 손실 및 월요일 바닥 매수 전략. 독점 기업으로서의 주가 부진 원인 분석.</t>
+          <t>반도체 섹터 약세 및 종목 자체 급락에 대한 우려. 보호예수, 프로그램 매도 등 하락 요인 언급. 간헐적 반등 기대.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체', '독점 기업']</t>
+          <t>['반도체', '보호예수', '하락']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2878,13 +2878,13 @@
         <v>1.45</v>
       </c>
       <c r="E27" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F27" t="n">
         <v>55</v>
       </c>
       <c r="G27" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H27" t="n">
         <v>4.8</v>
@@ -2910,7 +2910,7 @@
         <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>8419739063</v>
+        <v>8428018598</v>
       </c>
       <c r="P27" t="n">
         <v>5700</v>
@@ -2926,16 +2926,16 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>자금 납입 및 공시 관련 불확실성 속 하한가 하락 및 상폐 우려, 일부 매수세 유입 관찰.</t>
+          <t>하한가 기록 및 추가 하락 가능성 제기. 공시 지연 및 납입 관련 불확실성 언급. 상폐 가능성 우려 제기. 대규모 자금 유입 확인.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['하한가', '공시', '상폐']</t>
+          <t>['하한가', '공시', '납입']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9720</v>
+        <v>9640</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-35.20%</t>
+          <t>'-35.73%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="F28" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G28" t="n">
-        <v>920</v>
+        <v>936</v>
       </c>
       <c r="H28" t="n">
         <v>3.05</v>
@@ -2996,19 +2996,19 @@
         <v>12700</v>
       </c>
       <c r="M28" t="n">
-        <v>9620</v>
+        <v>9480</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>140196421725</v>
+        <v>142054471080</v>
       </c>
       <c r="P28" t="n">
         <v>12700</v>
       </c>
       <c r="Q28" t="n">
-        <v>9620</v>
+        <v>9480</v>
       </c>
       <c r="R28" t="n">
         <v>-41000</v>

--- a/data/trending_integrated_20261030_14.xlsx
+++ b/data/trending_integrated_20261030_14.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25650</v>
+        <v>29700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+185.00%</t>
+          <t>'+230.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="G2" t="n">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -601,7 +601,7 @@
         <v>19290</v>
       </c>
       <c r="L2" t="n">
-        <v>27100</v>
+        <v>29850</v>
       </c>
       <c r="M2" t="n">
         <v>16450</v>
@@ -610,10 +610,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>853207375015</v>
+        <v>922378139340</v>
       </c>
       <c r="P2" t="n">
-        <v>27100</v>
+        <v>29850</v>
       </c>
       <c r="Q2" t="n">
         <v>16450</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 관련 정부 지원 기대감 및 26년 IPO 대장 전망 언급. 13년 연속 흑자 기업으로 저평가 가능성 제기. 그러나 급락 패턴 반복 지적.</t>
+          <t>급등 후 변동성이 큰 상황으로, 매수 및 매도 시점에 대한 다양한 의견과 함께 개인 투자자들의 단타 접근에 대한 주의 요구.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', 'IPO', '흑자']</t>
+          <t>['급등', '변동성', '단타']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>상지건설</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7320</v>
+        <v>19410</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.31%</t>
+          <t>'+16.58%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="E3" t="n">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="G3" t="n">
-        <v>258</v>
+        <v>223</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6240</v>
+        <v>16650</v>
       </c>
       <c r="K3" t="n">
-        <v>6700</v>
+        <v>16830</v>
       </c>
       <c r="L3" t="n">
-        <v>7980</v>
+        <v>19900</v>
       </c>
       <c r="M3" t="n">
-        <v>6330</v>
+        <v>16750</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O3" t="n">
-        <v>38573317930</v>
+        <v>138878267640</v>
       </c>
       <c r="P3" t="n">
-        <v>16620</v>
+        <v>22450</v>
       </c>
       <c r="Q3" t="n">
-        <v>4600</v>
+        <v>6320</v>
       </c>
       <c r="R3" t="n">
-        <v>3000</v>
+        <v>69000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>급등 및 연상 기대감. 논현동, 천일고속, 동양건설 등 건설사 언급. 유증 성공 가능성 및 주포의 단기 시세 조종 의혹. 건설 산업 활성화에 따른 전망.</t>
+          <t>정부의 양자 보안 의무화 정책 수혜주로 주목받으며, 해킹 사태로 인한 반사이익 기대. 기술력과 향후 전망에 대한 긍정적 평가.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['급등', '유증', '주포']</t>
+          <t>['양자 보안', '수혜주', '해킹']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,178 +740,178 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>042940</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19450</v>
+        <v>2830</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.82%</t>
+          <t>'+15.51%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.75</v>
+        <v>0.16</v>
       </c>
       <c r="E4" t="n">
-        <v>161</v>
+        <v>58</v>
       </c>
       <c r="F4" t="n">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>214</v>
+        <v>40</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>0.79</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16650</v>
+        <v>2450</v>
       </c>
       <c r="K4" t="n">
-        <v>16830</v>
+        <v>2460</v>
       </c>
       <c r="L4" t="n">
-        <v>19900</v>
+        <v>3110</v>
       </c>
       <c r="M4" t="n">
-        <v>16750</v>
+        <v>2335</v>
       </c>
       <c r="N4" t="n">
-        <v>4.35</v>
+        <v>0.63</v>
       </c>
       <c r="O4" t="n">
-        <v>136935149460</v>
+        <v>13130715001</v>
       </c>
       <c r="P4" t="n">
-        <v>22450</v>
+        <v>3170</v>
       </c>
       <c r="Q4" t="n">
-        <v>6320</v>
+        <v>880</v>
       </c>
       <c r="R4" t="n">
-        <v>69000</v>
+        <v>-24000</v>
       </c>
       <c r="S4" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 양자 보안 의무화 및 해킹 사태 수혜주 부각. 기술력 및 신원 인증 중요성 강조. SGA솔루션즈 상한가 영향. 보안주 섹터 전반의 전망. 프로그램 매수세 및 계단식 하락 가능성 언급.</t>
+          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자 보안', '해킹', '수혜주']</t>
+          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>051630</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>상지건설</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8830</v>
+        <v>7180</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.68%</t>
+          <t>'+15.06%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>131</v>
+        <v>264</v>
       </c>
       <c r="H5" t="n">
-        <v>13.29</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7700</v>
+        <v>6240</v>
       </c>
       <c r="K5" t="n">
-        <v>9360</v>
+        <v>6700</v>
       </c>
       <c r="L5" t="n">
-        <v>9500</v>
+        <v>7980</v>
       </c>
       <c r="M5" t="n">
-        <v>8430</v>
+        <v>6330</v>
       </c>
       <c r="N5" t="n">
-        <v>12.92</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>10877469130</v>
+        <v>39709116120</v>
       </c>
       <c r="P5" t="n">
-        <v>13670</v>
+        <v>16620</v>
       </c>
       <c r="Q5" t="n">
-        <v>7060</v>
+        <v>4600</v>
       </c>
       <c r="R5" t="n">
-        <v>-44000</v>
+        <v>3000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>임상 3상 성공에도 불구하고 주가 부진. 시장 규모 및 경쟁 업체 고려 시 큰 호재 아님.</t>
+          <t>건설업 부활에 대한 기대감과 함께 급등 및 연상에 대한 언급. 유증 성공 여부 및 주가 움직임에 대한 관심 표출.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['임상 3상', '위식도염', '시장 규모']</t>
+          <t>['건설업', '급등', '유증']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,43 +919,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>003220</t>
+          <t>042940</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>진양화학</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2800</v>
+        <v>8780</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+14.29%</t>
+          <t>'+14.03%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>37</v>
+        <v>133</v>
       </c>
       <c r="H6" t="n">
-        <v>0.79</v>
+        <v>13.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2450</v>
+        <v>7700</v>
       </c>
       <c r="K6" t="n">
-        <v>2460</v>
+        <v>9360</v>
       </c>
       <c r="L6" t="n">
-        <v>3110</v>
+        <v>9500</v>
       </c>
       <c r="M6" t="n">
-        <v>2335</v>
+        <v>8430</v>
       </c>
       <c r="N6" t="n">
-        <v>0.63</v>
+        <v>12.92</v>
       </c>
       <c r="O6" t="n">
-        <v>13059988571</v>
+        <v>11001833325</v>
       </c>
       <c r="P6" t="n">
-        <v>3170</v>
+        <v>13670</v>
       </c>
       <c r="Q6" t="n">
-        <v>880</v>
+        <v>7060</v>
       </c>
       <c r="R6" t="n">
-        <v>-24000</v>
+        <v>-44000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
+          <t>임상 3상 성공에도 불구하고 주가 부진. 시장 규모 및 경쟁 업체 고려 시 큰 호재 아님.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
+          <t>['임상 3상', '위식도염', '시장 규모']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>051630</t>
+          <t>003220</t>
         </is>
       </c>
     </row>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15810</v>
+        <v>15760</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.54%</t>
+          <t>'+5.21%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="H7" t="n">
         <v>7.15</v>
@@ -1070,7 +1070,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>56406361710</v>
+        <v>57060477395</v>
       </c>
       <c r="P7" t="n">
         <v>49800</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51600</v>
+        <v>51300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.09%</t>
+          <t>'+4.48%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.82</v>
       </c>
       <c r="E8" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F8" t="n">
         <v>68</v>
       </c>
       <c r="G8" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H8" t="n">
         <v>23.82</v>
@@ -1162,7 +1162,7 @@
         <v>24.64</v>
       </c>
       <c r="O8" t="n">
-        <v>70048042900</v>
+        <v>71513889800</v>
       </c>
       <c r="P8" t="n">
         <v>97900</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>TC본더 매출 본격화 및 공매도 타격 전망. 사상 최대 실적 발표 기반 하락 후 반등 기대. 한미반도체와 비교하며 저평가 주장.</t>
+          <t>TC본더 매출 본격화 및 공매도 숏커버링 기대감 속에 사상 최대 실적 발표. 경쟁사 대비 저평가 및 HBM 시대 수혜 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['TC본더', '실적', '공매도']</t>
+          <t>['TC본더', '실적', 'HBM']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>서울반도체</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11760</v>
+        <v>29150</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.00%</t>
+          <t>'+3.92%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.04</v>
+        <v>-0.36</v>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>85</v>
       </c>
       <c r="F9" t="n">
-        <v>202</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>1009</v>
+        <v>393</v>
       </c>
       <c r="H9" t="n">
-        <v>15.04</v>
+        <v>4.69</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>11200</v>
+        <v>28050</v>
       </c>
       <c r="K9" t="n">
-        <v>13500</v>
+        <v>27850</v>
       </c>
       <c r="L9" t="n">
-        <v>13710</v>
+        <v>30400</v>
       </c>
       <c r="M9" t="n">
-        <v>11620</v>
+        <v>27650</v>
       </c>
       <c r="N9" t="n">
-        <v>15.08</v>
+        <v>5.05</v>
       </c>
       <c r="O9" t="n">
-        <v>59930801310</v>
+        <v>129135727250</v>
       </c>
       <c r="P9" t="n">
-        <v>18960</v>
+        <v>50600</v>
       </c>
       <c r="Q9" t="n">
-        <v>5730</v>
+        <v>13210</v>
       </c>
       <c r="R9" t="n">
-        <v>-423000</v>
+        <v>-40000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>228000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>세계 1위 희토류 없는 백색 LED 개발 및 기술력 강조. 100억 달러 시장 석권 기대. 공매도 제도 폐지 요구. 주당 10만원 이상 정상 가격 제시. 반등 및 우상향 전망.</t>
+          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['백색 LED', '희토류', '공매도']</t>
+          <t>['로봇', '엑추에이터', '반도체']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>046890</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>서울반도체</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29000</v>
+        <v>11450</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.39%</t>
+          <t>'+2.23%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.36</v>
+        <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>361</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>204</v>
       </c>
       <c r="G10" t="n">
-        <v>389</v>
+        <v>1014</v>
       </c>
       <c r="H10" t="n">
-        <v>4.69</v>
+        <v>15.04</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>28050</v>
+        <v>11200</v>
       </c>
       <c r="K10" t="n">
-        <v>27850</v>
+        <v>13500</v>
       </c>
       <c r="L10" t="n">
-        <v>30400</v>
+        <v>13710</v>
       </c>
       <c r="M10" t="n">
-        <v>27650</v>
+        <v>11420</v>
       </c>
       <c r="N10" t="n">
-        <v>5.05</v>
+        <v>15.08</v>
       </c>
       <c r="O10" t="n">
-        <v>127917470525</v>
+        <v>61698186070</v>
       </c>
       <c r="P10" t="n">
-        <v>50600</v>
+        <v>18960</v>
       </c>
       <c r="Q10" t="n">
-        <v>13210</v>
+        <v>5730</v>
       </c>
       <c r="R10" t="n">
-        <v>-40000</v>
+        <v>-423000</v>
       </c>
       <c r="S10" t="n">
-        <v>228000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
+          <t>세계 1위 희토류 없는 백색 LED 개발 및 기술력 강조. 100억 달러 시장 석권 기대. 공매도 제도 폐지 요구. 주당 10만원 이상 정상 가격 제시. 반등 및 우상향 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['로봇', '엑추에이터', '반도체']</t>
+          <t>['백색 LED', '희토류', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>046890</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15730</v>
+        <v>15750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.06%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F11" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G11" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H11" t="n">
         <v>28.13</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>57483838265</v>
+        <v>59196743540</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4005</v>
+        <v>3995</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.87%</t>
+          <t>'-1.11%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H12" t="n">
         <v>1.43</v>
@@ -1530,7 +1530,7 @@
         <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>83209405871</v>
+        <v>83696450786</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7280</v>
+        <v>7265</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.28%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
         <v>30</v>
       </c>
       <c r="G13" t="n">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="H13" t="n">
         <v>25.3</v>
@@ -1622,7 +1622,7 @@
         <v>25.32</v>
       </c>
       <c r="O13" t="n">
-        <v>11297715840</v>
+        <v>11818903370</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60900</v>
+        <v>60600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.03%</t>
+          <t>'-3.50%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G14" t="n">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="H14" t="n">
         <v>41.76</v>
@@ -1714,7 +1714,7 @@
         <v>41.55</v>
       </c>
       <c r="O14" t="n">
-        <v>104966693450</v>
+        <v>108018665850</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1759,307 +1759,307 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6370</v>
+        <v>222250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.07%</t>
+          <t>'-4.20%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>74</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>494</v>
       </c>
       <c r="G15" t="n">
-        <v>86</v>
+        <v>1165</v>
       </c>
       <c r="H15" t="n">
-        <v>0.85</v>
+        <v>46.17</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6640</v>
+        <v>232000</v>
       </c>
       <c r="K15" t="n">
-        <v>7210</v>
+        <v>223500</v>
       </c>
       <c r="L15" t="n">
-        <v>7500</v>
+        <v>229500</v>
       </c>
       <c r="M15" t="n">
-        <v>6230</v>
+        <v>216500</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9</v>
+        <v>46.19</v>
       </c>
       <c r="O15" t="n">
-        <v>32334016890</v>
+        <v>3280238174500</v>
       </c>
       <c r="P15" t="n">
-        <v>9820</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>4000</v>
+        <v>94500</v>
       </c>
       <c r="R15" t="n">
-        <v>-27000</v>
+        <v>538000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>정치적 이슈와 경영진 관련 비판이 주를 이루며, 주가 부양책 부재에 대한 불만이 제기됨. 일론 머스크 언급 등 비교 대상에 대한 아쉬움 표현.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['경영진', '주가 부양', '자사주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>222500</v>
+        <v>6360</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.09%</t>
+          <t>'-4.22%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>75</v>
       </c>
       <c r="F16" t="n">
-        <v>498</v>
+        <v>38</v>
       </c>
       <c r="G16" t="n">
-        <v>1138</v>
+        <v>87</v>
       </c>
       <c r="H16" t="n">
-        <v>46.17</v>
+        <v>0.85</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>232000</v>
+        <v>6640</v>
       </c>
       <c r="K16" t="n">
-        <v>223500</v>
+        <v>7210</v>
       </c>
       <c r="L16" t="n">
-        <v>229500</v>
+        <v>7500</v>
       </c>
       <c r="M16" t="n">
-        <v>216500</v>
+        <v>6230</v>
       </c>
       <c r="N16" t="n">
-        <v>46.19</v>
+        <v>0.9</v>
       </c>
       <c r="O16" t="n">
-        <v>3210313834000</v>
+        <v>32401355840</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>9820</v>
       </c>
       <c r="Q16" t="n">
-        <v>94500</v>
+        <v>4000</v>
       </c>
       <c r="R16" t="n">
-        <v>538000</v>
+        <v>-27000</v>
       </c>
       <c r="S16" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>이재용 경영 퇴출 및 자사주 매입/소각 요구. 일론 머스크와 비교하며 시총 상승 기대 언급. 정치적 발언 다수.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['자사주', '이재용', '시총']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8210</v>
+        <v>22400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.31%</t>
+          <t>'-5.08%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01</v>
+        <v>-0.63</v>
       </c>
       <c r="E17" t="n">
-        <v>118</v>
+        <v>274</v>
       </c>
       <c r="F17" t="n">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="G17" t="n">
-        <v>312</v>
+        <v>654</v>
       </c>
       <c r="H17" t="n">
-        <v>2.67</v>
+        <v>11.6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8580</v>
+        <v>23600</v>
       </c>
       <c r="K17" t="n">
-        <v>11090</v>
+        <v>22650</v>
       </c>
       <c r="L17" t="n">
-        <v>11150</v>
+        <v>22750</v>
       </c>
       <c r="M17" t="n">
-        <v>8070</v>
+        <v>21100</v>
       </c>
       <c r="N17" t="n">
-        <v>2.66</v>
+        <v>12.23</v>
       </c>
       <c r="O17" t="n">
-        <v>30336950410</v>
+        <v>95370886850</v>
       </c>
       <c r="P17" t="n">
-        <v>19270</v>
+        <v>59300</v>
       </c>
       <c r="Q17" t="n">
-        <v>2135</v>
+        <v>21100</v>
       </c>
       <c r="R17" t="n">
-        <v>-396000</v>
+        <v>-728000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-220000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>서울바이오시스의 독점 기술 및 신규 기술(광통신, 와이캅3)에 대한 기대감 존재. 환기 문제 해소 및 외인 유입 가능성 언급.</t>
+          <t>한화솔루션의 주가 급락에 대한 의혹 제기. RE100 승인 및 카터스빌 물량 완판 소식에도 불구하고 주가 부진. 실적 턴어라운드에도 불구하고 주가 하락.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광반도체', '와이캅3', '환기']</t>
+          <t>['주가 누르기', 'RE100', '실적 턴어라운드']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22450</v>
+        <v>53700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.87%</t>
+          <t>'-5.29%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.63</v>
+        <v>-0.2</v>
       </c>
       <c r="E18" t="n">
-        <v>273</v>
+        <v>383</v>
       </c>
       <c r="F18" t="n">
-        <v>177</v>
+        <v>242</v>
       </c>
       <c r="G18" t="n">
-        <v>647</v>
+        <v>1271</v>
       </c>
       <c r="H18" t="n">
-        <v>11.6</v>
+        <v>22.14</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>23600</v>
+        <v>56700</v>
       </c>
       <c r="K18" t="n">
-        <v>22650</v>
+        <v>55500</v>
       </c>
       <c r="L18" t="n">
-        <v>22750</v>
+        <v>55900</v>
       </c>
       <c r="M18" t="n">
-        <v>21100</v>
+        <v>53700</v>
       </c>
       <c r="N18" t="n">
-        <v>12.23</v>
+        <v>22.34</v>
       </c>
       <c r="O18" t="n">
-        <v>93300076475</v>
+        <v>98017710700</v>
       </c>
       <c r="P18" t="n">
-        <v>59300</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>21100</v>
+        <v>53400</v>
       </c>
       <c r="R18" t="n">
-        <v>-728000</v>
+        <v>-281000</v>
       </c>
       <c r="S18" t="n">
-        <v>-220000</v>
+        <v>-89000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>한화솔루션의 주가 급락에 대한 의혹 제기. RE100 승인 및 카터스빌 물량 완판 소식에도 불구하고 주가 부진. 실적 턴어라운드에도 불구하고 주가 하락.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 관련 긍정적 언급. 다만, 정부 정책 및 시장 상황에 대한 부정적 평가가 sentiment에 영향을 미치며 fact score는 구체적인 수주 내용을 기반으로 산정.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 누르기', 'RE100', '실적 턴어라운드']</t>
+          <t>['SMR', '원자로 수주', '실적']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,99 +2120,99 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>53800</v>
+        <v>8110</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.11%</t>
+          <t>'-5.48%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.2</v>
+        <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>370</v>
+        <v>118</v>
       </c>
       <c r="F19" t="n">
-        <v>239</v>
+        <v>68</v>
       </c>
       <c r="G19" t="n">
-        <v>1218</v>
+        <v>318</v>
       </c>
       <c r="H19" t="n">
-        <v>22.14</v>
+        <v>2.67</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>56700</v>
+        <v>8580</v>
       </c>
       <c r="K19" t="n">
-        <v>55500</v>
+        <v>11090</v>
       </c>
       <c r="L19" t="n">
-        <v>55900</v>
+        <v>11150</v>
       </c>
       <c r="M19" t="n">
-        <v>53700</v>
+        <v>8070</v>
       </c>
       <c r="N19" t="n">
-        <v>22.34</v>
+        <v>2.66</v>
       </c>
       <c r="O19" t="n">
-        <v>95393615550</v>
+        <v>30499039220</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>19270</v>
       </c>
       <c r="Q19" t="n">
-        <v>53400</v>
+        <v>2135</v>
       </c>
       <c r="R19" t="n">
-        <v>-281000</v>
+        <v>-396000</v>
       </c>
       <c r="S19" t="n">
-        <v>-89000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 관련 긍정적 언급. 다만, 정부 정책 및 시장 상황에 대한 부정적 평가가 sentiment에 영향을 미치며 fact score는 구체적인 수주 내용을 기반으로 산정.</t>
+          <t>서울바이오시스의 독점 기술 및 신규 기술(광통신, 와이캅3)에 대한 기대감 존재. 환기 문제 해소 및 외인 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['SMR', '원자로 수주', '실적']</t>
+          <t>['광반도체', '와이캅3', '환기']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>173400</v>
+        <v>173300</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.71%</t>
+          <t>'-5.76%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F20" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G20" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="H20" t="n">
         <v>74.87</v>
@@ -2266,7 +2266,7 @@
         <v>75</v>
       </c>
       <c r="O20" t="n">
-        <v>683994853500</v>
+        <v>697412480400</v>
       </c>
       <c r="P20" t="n">
         <v>243500</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10910</v>
+        <v>10860</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.11%</t>
+          <t>'-6.54%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F21" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G21" t="n">
-        <v>1417</v>
+        <v>1448</v>
       </c>
       <c r="H21" t="n">
         <v>9.73</v>
@@ -2352,13 +2352,13 @@
         <v>11470</v>
       </c>
       <c r="M21" t="n">
-        <v>10880</v>
+        <v>10850</v>
       </c>
       <c r="N21" t="n">
         <v>9.6</v>
       </c>
       <c r="O21" t="n">
-        <v>61891545970</v>
+        <v>63425548565</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1417000</v>
+        <v>1415000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.14%</t>
+          <t>'-7.27%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="G22" t="n">
-        <v>1205</v>
+        <v>1180</v>
       </c>
       <c r="H22" t="n">
         <v>48.72</v>
@@ -2450,7 +2450,7 @@
         <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>3858849720000</v>
+        <v>3974510017500</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>종가 150 기대감 및 반등 가능성 언급. 샌디스크 서프라이즈, AI 투자 확대, 자사주 매입 호재 가능성 제기. 외인 매수세 주목.</t>
+          <t>반도체 업황 개선 기대감과 함께 자사주 매입 및 AI 투자 확대 수혜 전망. 긍정적 수급 및 종가 상승에 대한 기대감 표출.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['자사주', 'AI', '외인']</t>
+          <t>['AI 투자', '자사주 매입', '반도체 업황']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13800</v>
+        <v>13740</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.18%</t>
+          <t>'-8.58%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F23" t="n">
         <v>69</v>
       </c>
       <c r="G23" t="n">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>48710948835</v>
+        <v>49595548300</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7090</v>
+        <v>7060</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.25%</t>
+          <t>'-10.63%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G24" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>17121697270</v>
+        <v>17281837110</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>117400</v>
+        <v>118150</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-15.05%</t>
+          <t>'-14.51%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F25" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G25" t="n">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2726,7 +2726,7 @@
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>194114335000</v>
+        <v>198083399700</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13620</v>
+        <v>13590</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-19.88%</t>
+          <t>'-20.06%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="F26" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G26" t="n">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>68952312600</v>
+        <v>69701752020</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>반도체 섹터 약세 및 종목 자체 급락에 대한 우려. 보호예수, 프로그램 매도 등 하락 요인 언급. 간헐적 반등 기대.</t>
+          <t>보호예수 물량 출회와 시장 상황 악화로 인한 주가 하락에 대한 불만 표출. 급락 및 하한가 가능성에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['반도체', '보호예수', '하락']</t>
+          <t>['보호예수', '급락', '시장 상황']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2878,13 +2878,13 @@
         <v>1.45</v>
       </c>
       <c r="E27" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F27" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G27" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H27" t="n">
         <v>4.8</v>
@@ -2910,7 +2910,7 @@
         <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>8428018598</v>
+        <v>8479699358</v>
       </c>
       <c r="P27" t="n">
         <v>5700</v>
@@ -2926,16 +2926,16 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>하한가 기록 및 추가 하락 가능성 제기. 공시 지연 및 납입 관련 불확실성 언급. 상폐 가능성 우려 제기. 대규모 자금 유입 확인.</t>
+          <t>신규 상장 후 급락세가 지속되며 하한가를 기록, 상폐 가능성에 대한 우려가 커짐. 납입 지연 및 부정적 전망이 지배적.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['하한가', '공시', '납입']</t>
+          <t>['상폐', '하한가', '신규 상장']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9640</v>
+        <v>9900</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-35.73%</t>
+          <t>'-34.00%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>558</v>
+        <v>573</v>
       </c>
       <c r="F28" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G28" t="n">
-        <v>936</v>
+        <v>960</v>
       </c>
       <c r="H28" t="n">
         <v>3.05</v>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>142054471080</v>
+        <v>144179823805</v>
       </c>
       <c r="P28" t="n">
         <v>12700</v>

--- a/data/trending_integrated_20261030_14.xlsx
+++ b/data/trending_integrated_20261030_14.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29700</v>
+        <v>31800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+230.00%</t>
+          <t>'+253.33%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="G2" t="n">
-        <v>804</v>
+        <v>723</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -601,7 +601,7 @@
         <v>19290</v>
       </c>
       <c r="L2" t="n">
-        <v>29850</v>
+        <v>33800</v>
       </c>
       <c r="M2" t="n">
         <v>16450</v>
@@ -610,10 +610,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>922378139340</v>
+        <v>1019541969690</v>
       </c>
       <c r="P2" t="n">
-        <v>29850</v>
+        <v>33800</v>
       </c>
       <c r="Q2" t="n">
         <v>16450</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>급등 후 변동성이 큰 상황으로, 매수 및 매도 시점에 대한 다양한 의견과 함께 개인 투자자들의 단타 접근에 대한 주의 요구.</t>
+          <t>정부의 AI 지원 및 26년 IPO 대장 기대감 속 급등, 투자자들에게 단타 자제 및 보유 권유.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['급등', '변동성', '단타']</t>
+          <t>['AI', 'IPO', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19410</v>
+        <v>19330</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.58%</t>
+          <t>'+16.10%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.75</v>
       </c>
       <c r="E3" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F3" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G3" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="H3" t="n">
         <v>3.6</v>
@@ -702,7 +702,7 @@
         <v>4.35</v>
       </c>
       <c r="O3" t="n">
-        <v>138878267640</v>
+        <v>140172472165</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>진양화학</t>
+          <t>상지건설</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2830</v>
+        <v>7170</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.51%</t>
+          <t>'+14.90%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>270</v>
       </c>
       <c r="H4" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2450</v>
+        <v>6240</v>
       </c>
       <c r="K4" t="n">
-        <v>2460</v>
+        <v>6700</v>
       </c>
       <c r="L4" t="n">
-        <v>3110</v>
+        <v>7980</v>
       </c>
       <c r="M4" t="n">
-        <v>2335</v>
+        <v>6330</v>
       </c>
       <c r="N4" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>13130715001</v>
+        <v>40290055890</v>
       </c>
       <c r="P4" t="n">
-        <v>3170</v>
+        <v>16620</v>
       </c>
       <c r="Q4" t="n">
-        <v>880</v>
+        <v>4600</v>
       </c>
       <c r="R4" t="n">
-        <v>-24000</v>
+        <v>3000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
+          <t>청담동 빌라 건설, 3천억 재료 언급하며 급등세, 건설업 회생 및 국가 경제 활성화 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
+          <t>['건설', '재료', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,91 +827,91 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>051630</t>
+          <t>042940</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>상지건설</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7180</v>
+        <v>2790</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.06%</t>
+          <t>'+13.88%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="E5" t="n">
-        <v>127</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>264</v>
+        <v>40</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6240</v>
+        <v>2450</v>
       </c>
       <c r="K5" t="n">
-        <v>6700</v>
+        <v>2460</v>
       </c>
       <c r="L5" t="n">
-        <v>7980</v>
+        <v>3110</v>
       </c>
       <c r="M5" t="n">
-        <v>6330</v>
+        <v>2335</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="O5" t="n">
-        <v>39709116120</v>
+        <v>13204671081</v>
       </c>
       <c r="P5" t="n">
-        <v>16620</v>
+        <v>3170</v>
       </c>
       <c r="Q5" t="n">
-        <v>4600</v>
+        <v>880</v>
       </c>
       <c r="R5" t="n">
-        <v>3000</v>
+        <v>-24000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>건설업 부활에 대한 기대감과 함께 급등 및 연상에 대한 언급. 유증 성공 여부 및 주가 움직임에 대한 관심 표출.</t>
+          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['건설업', '급등', '유증']</t>
+          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,12 +919,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>042940</t>
+          <t>051630</t>
         </is>
       </c>
     </row>
@@ -935,18 +935,18 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8780</v>
+        <v>8710</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+14.03%</t>
+          <t>'+13.12%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
         <v>43</v>
@@ -978,7 +978,7 @@
         <v>12.92</v>
       </c>
       <c r="O6" t="n">
-        <v>11001833325</v>
+        <v>11119802810</v>
       </c>
       <c r="P6" t="n">
         <v>13670</v>
@@ -1038,13 +1038,13 @@
         <v>-0.9</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F7" t="n">
         <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="H7" t="n">
         <v>7.15</v>
@@ -1070,7 +1070,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>57060477395</v>
+        <v>57970192565</v>
       </c>
       <c r="P7" t="n">
         <v>49800</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51300</v>
+        <v>51500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.48%</t>
+          <t>'+4.89%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.82</v>
       </c>
       <c r="E8" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F8" t="n">
         <v>68</v>
       </c>
       <c r="G8" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H8" t="n">
         <v>23.82</v>
@@ -1162,7 +1162,7 @@
         <v>24.64</v>
       </c>
       <c r="O8" t="n">
-        <v>71513889800</v>
+        <v>72899567600</v>
       </c>
       <c r="P8" t="n">
         <v>97900</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>TC본더 매출 본격화 및 공매도 숏커버링 기대감 속에 사상 최대 실적 발표. 경쟁사 대비 저평가 및 HBM 시대 수혜 전망.</t>
+          <t>TC본더 매출 본격화 및 사이버 해킹 보안 수혜 기대감 속 실적 발표. 다만, 한미반도체와의 시가총액 비교 및 '곧 폭포수 쏟아진다'는 부정적 전망 혼재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['TC본더', '실적', 'HBM']</t>
+          <t>['TC본더', '실적', '시가총액']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29150</v>
+        <v>29350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.92%</t>
+          <t>'+4.63%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.36</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="H9" t="n">
         <v>4.69</v>
@@ -1254,7 +1254,7 @@
         <v>5.05</v>
       </c>
       <c r="O9" t="n">
-        <v>129135727250</v>
+        <v>131369668275</v>
       </c>
       <c r="P9" t="n">
         <v>50600</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11450</v>
+        <v>11350</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.23%</t>
+          <t>'+1.34%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="F10" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G10" t="n">
-        <v>1014</v>
+        <v>1040</v>
       </c>
       <c r="H10" t="n">
         <v>15.04</v>
@@ -1340,13 +1340,13 @@
         <v>13710</v>
       </c>
       <c r="M10" t="n">
-        <v>11420</v>
+        <v>11300</v>
       </c>
       <c r="N10" t="n">
         <v>15.08</v>
       </c>
       <c r="O10" t="n">
-        <v>61698186070</v>
+        <v>63151819585</v>
       </c>
       <c r="P10" t="n">
         <v>18960</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15750</v>
+        <v>15700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.19%</t>
+          <t>'-0.13%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F11" t="n">
         <v>73</v>
       </c>
       <c r="G11" t="n">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="H11" t="n">
         <v>28.13</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>59196743540</v>
+        <v>60977648015</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3분기 실적 서프라이즈 및 미국 조선주 강세 속 국내 조선주 약세 진단. 정기선 승계와 증여세 상관관계 의문 제기.</t>
+          <t>3분기 실적 호조 및 미국 조선주 강세에도 불구하고 국내 조선주 약세, 정기선 승계 및 증여세 이슈 언급. 델핀FLNG 2호기 수주 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['실적', '조선주', '승계']</t>
+          <t>['실적', '조선주', 'FLNG']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3995</v>
+        <v>3960</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.11%</t>
+          <t>'-1.98%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H12" t="n">
         <v>1.43</v>
@@ -1530,7 +1530,7 @@
         <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>83696450786</v>
+        <v>84414010313</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7265</v>
+        <v>7240</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'-2.82%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H13" t="n">
         <v>25.3</v>
@@ -1616,13 +1616,13 @@
         <v>7570</v>
       </c>
       <c r="M13" t="n">
-        <v>7250</v>
+        <v>7230</v>
       </c>
       <c r="N13" t="n">
         <v>25.32</v>
       </c>
       <c r="O13" t="n">
-        <v>11818903370</v>
+        <v>12831315765</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1682,13 +1682,13 @@
         <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G14" t="n">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="H14" t="n">
         <v>41.76</v>
@@ -1714,7 +1714,7 @@
         <v>41.55</v>
       </c>
       <c r="O14" t="n">
-        <v>108018665850</v>
+        <v>111035720300</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>222250</v>
+        <v>222000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.20%</t>
+          <t>'-4.31%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G15" t="n">
-        <v>1165</v>
+        <v>1131</v>
       </c>
       <c r="H15" t="n">
         <v>46.17</v>
@@ -1806,7 +1806,7 @@
         <v>46.19</v>
       </c>
       <c r="O15" t="n">
-        <v>3280238174500</v>
+        <v>3351777159250</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 이슈와 경영진 관련 비판이 주를 이루며, 주가 부양책 부재에 대한 불만이 제기됨. 일론 머스크 언급 등 비교 대상에 대한 아쉬움 표현.</t>
+          <t>이재용 전 회장의 경영 복귀 및 주주 환원 정책에 대한 비판적 의견과 정치적 발언이 혼재된 게시글.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['경영진', '주가 부양', '자사주']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6360</v>
+        <v>6350</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.22%</t>
+          <t>'-4.37%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1898,7 +1898,7 @@
         <v>0.9</v>
       </c>
       <c r="O16" t="n">
-        <v>32401355840</v>
+        <v>32499871150</v>
       </c>
       <c r="P16" t="n">
         <v>9820</v>
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22400</v>
+        <v>53600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.08%</t>
+          <t>'-5.47%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.63</v>
+        <v>-0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>274</v>
+        <v>394</v>
       </c>
       <c r="F17" t="n">
-        <v>177</v>
+        <v>249</v>
       </c>
       <c r="G17" t="n">
-        <v>654</v>
+        <v>1297</v>
       </c>
       <c r="H17" t="n">
-        <v>11.6</v>
+        <v>22.14</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>23600</v>
+        <v>56700</v>
       </c>
       <c r="K17" t="n">
-        <v>22650</v>
+        <v>55500</v>
       </c>
       <c r="L17" t="n">
-        <v>22750</v>
+        <v>55900</v>
       </c>
       <c r="M17" t="n">
-        <v>21100</v>
+        <v>53500</v>
       </c>
       <c r="N17" t="n">
-        <v>12.23</v>
+        <v>22.34</v>
       </c>
       <c r="O17" t="n">
-        <v>95370886850</v>
+        <v>104291010850</v>
       </c>
       <c r="P17" t="n">
-        <v>59300</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>21100</v>
+        <v>53400</v>
       </c>
       <c r="R17" t="n">
-        <v>-728000</v>
+        <v>-281000</v>
       </c>
       <c r="S17" t="n">
-        <v>-220000</v>
+        <v>-89000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>한화솔루션의 주가 급락에 대한 의혹 제기. RE100 승인 및 카터스빌 물량 완판 소식에도 불구하고 주가 부진. 실적 턴어라운드에도 불구하고 주가 하락.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 호조 관련 소식에도 불구하고 주가 하락, 정부 정책 및 체코 원전 사업 관련 비판.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 누르기', 'RE100', '실적 턴어라운드']</t>
+          <t>['SMR', '뉴스케일파워', '원전']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53700</v>
+        <v>22300</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.29%</t>
+          <t>'-5.51%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.2</v>
+        <v>-0.63</v>
       </c>
       <c r="E18" t="n">
-        <v>383</v>
+        <v>275</v>
       </c>
       <c r="F18" t="n">
-        <v>242</v>
+        <v>178</v>
       </c>
       <c r="G18" t="n">
-        <v>1271</v>
+        <v>665</v>
       </c>
       <c r="H18" t="n">
-        <v>22.14</v>
+        <v>11.6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>56700</v>
+        <v>23600</v>
       </c>
       <c r="K18" t="n">
-        <v>55500</v>
+        <v>22650</v>
       </c>
       <c r="L18" t="n">
-        <v>55900</v>
+        <v>22750</v>
       </c>
       <c r="M18" t="n">
-        <v>53700</v>
+        <v>21100</v>
       </c>
       <c r="N18" t="n">
-        <v>22.34</v>
+        <v>12.23</v>
       </c>
       <c r="O18" t="n">
-        <v>98017710700</v>
+        <v>97400899150</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>59300</v>
       </c>
       <c r="Q18" t="n">
-        <v>53400</v>
+        <v>21100</v>
       </c>
       <c r="R18" t="n">
-        <v>-281000</v>
+        <v>-728000</v>
       </c>
       <c r="S18" t="n">
-        <v>-89000</v>
+        <v>-220000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 관련 긍정적 언급. 다만, 정부 정책 및 시장 상황에 대한 부정적 평가가 sentiment에 영향을 미치며 fact score는 구체적인 수주 내용을 기반으로 산정.</t>
+          <t>RE100 1조원 승인 및 미국 카터스빌 모듈 완판 소식에도 불구하고 주가 하락 및 유증에 대한 불만, 의도적 주가 누르기 의혹 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['SMR', '원자로 수주', '실적']</t>
+          <t>['RE100', '카터스빌', '유증']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8110</v>
+        <v>8100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.48%</t>
+          <t>'-5.59%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F19" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G19" t="n">
         <v>318</v>
@@ -2168,13 +2168,13 @@
         <v>11150</v>
       </c>
       <c r="M19" t="n">
-        <v>8070</v>
+        <v>8050</v>
       </c>
       <c r="N19" t="n">
         <v>2.66</v>
       </c>
       <c r="O19" t="n">
-        <v>30499039220</v>
+        <v>30702226415</v>
       </c>
       <c r="P19" t="n">
         <v>19270</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>173300</v>
+        <v>172800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.76%</t>
+          <t>'-6.04%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F20" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G20" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H20" t="n">
         <v>74.87</v>
@@ -2266,7 +2266,7 @@
         <v>75</v>
       </c>
       <c r="O20" t="n">
-        <v>697412480400</v>
+        <v>714801652400</v>
       </c>
       <c r="P20" t="n">
         <v>243500</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10860</v>
+        <v>10830</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.54%</t>
+          <t>'-6.80%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="F21" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="G21" t="n">
-        <v>1448</v>
+        <v>1479</v>
       </c>
       <c r="H21" t="n">
         <v>9.73</v>
@@ -2352,13 +2352,13 @@
         <v>11470</v>
       </c>
       <c r="M21" t="n">
-        <v>10850</v>
+        <v>10820</v>
       </c>
       <c r="N21" t="n">
         <v>9.6</v>
       </c>
       <c r="O21" t="n">
-        <v>63425548565</v>
+        <v>64949696785</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1415000</v>
+        <v>1409000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.27%</t>
+          <t>'-7.67%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="G22" t="n">
-        <v>1180</v>
+        <v>1190</v>
       </c>
       <c r="H22" t="n">
         <v>48.72</v>
@@ -2450,7 +2450,7 @@
         <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>3974510017500</v>
+        <v>4049458041500</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>반도체 업황 개선 기대감과 함께 자사주 매입 및 AI 투자 확대 수혜 전망. 긍정적 수급 및 종가 상승에 대한 기대감 표출.</t>
+          <t>샌디스크 서프라이즈 및 AI 투자 확대 기대감 속 자사주 매입 소식에도 불구하고 주가 하락, 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['AI 투자', '자사주 매입', '반도체 업황']</t>
+          <t>['AI', '자사주 매입', '실적']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13740</v>
+        <v>13700</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.58%</t>
+          <t>'-8.85%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2516,7 +2516,7 @@
         <v>69</v>
       </c>
       <c r="G23" t="n">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>49595548300</v>
+        <v>50193585120</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세 및 루닛 사례 언급하며 국내 증시 불신 속 호재 다수 존재 주장. 27년까지 목표가 29000원 제시. 공매도 세력 비판.</t>
+          <t>27년까지의 성장 전망 및 광통신 섹터 호재에도 불구하고 국내 증시 불신으로 인한 주가 하락, 공매도 세력 비판.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['광통신', '호재', '공매도']</t>
+          <t>['광통신', '특허', '호재']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7060</v>
+        <v>7020</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.63%</t>
+          <t>'-11.14%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F24" t="n">
         <v>42</v>
       </c>
       <c r="G24" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2628,13 +2628,13 @@
         <v>8130</v>
       </c>
       <c r="M24" t="n">
-        <v>7050</v>
+        <v>7010</v>
       </c>
       <c r="N24" t="n">
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>17281837110</v>
+        <v>17648520590</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>118150</v>
+        <v>118300</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-14.51%</t>
+          <t>'-14.40%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="F25" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G25" t="n">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2726,7 +2726,7 @@
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>198083399700</v>
+        <v>201068601450</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13590</v>
+        <v>13460</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-20.06%</t>
+          <t>'-20.82%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F26" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G26" t="n">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>69701752020</v>
+        <v>70649707715</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회와 시장 상황 악화로 인한 주가 하락에 대한 불만 표출. 급락 및 하한가 가능성에 대한 우려 제기.</t>
+          <t>보호예수 물량 출회 및 반도체 섹터 약세 속 주가 하락, 개인 투자자들의 매매 어려움 토로.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '급락', '시장 상황']</t>
+          <t>['보호예수', '반도체', '하한가']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2884,7 +2884,7 @@
         <v>57</v>
       </c>
       <c r="G27" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H27" t="n">
         <v>4.8</v>
@@ -2910,7 +2910,7 @@
         <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>8479699358</v>
+        <v>8489258638</v>
       </c>
       <c r="P27" t="n">
         <v>5700</v>
@@ -2926,16 +2926,16 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>신규 상장 후 급락세가 지속되며 하한가를 기록, 상폐 가능성에 대한 우려가 커짐. 납입 지연 및 부정적 전망이 지배적.</t>
+          <t>하한가 기록, 상폐 우려 및 자금 납입 지연 가능성 언급, 공시 및 납입 여부에 따른 주가 변동성 예상.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['상폐', '하한가', '신규 상장']</t>
+          <t>['하한가', '상폐', '납입']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9900</v>
+        <v>9800</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-34.00%</t>
+          <t>'-34.67%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>573</v>
+        <v>600</v>
       </c>
       <c r="F28" t="n">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="G28" t="n">
-        <v>960</v>
+        <v>981</v>
       </c>
       <c r="H28" t="n">
         <v>3.05</v>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>144179823805</v>
+        <v>148306657755</v>
       </c>
       <c r="P28" t="n">
         <v>12700</v>
